--- a/research/traditional_assets/database/data/czech_republic/czech_republic_shoe.xlsx
+++ b/research/traditional_assets/database/data/czech_republic/czech_republic_shoe.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09055410850237572</v>
+        <v>0.09041850569622123</v>
       </c>
       <c r="C2">
-        <v>12.98450246339582</v>
+        <v>12.86318866257173</v>
       </c>
       <c r="D2">
-        <v>11.63450246339582</v>
+        <v>11.64328866257173</v>
       </c>
       <c r="E2">
-        <v>-1.91</v>
+        <v>-1.7799</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1301</v>
       </c>
       <c r="G2">
         <v>1.35</v>
@@ -1451,28 +1451,28 @@
         <v>2.151</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.006544029999999999</v>
       </c>
       <c r="N2">
-        <v>2.151</v>
+        <v>2.14445597</v>
       </c>
       <c r="O2">
-        <v>0.4086899999999999</v>
+        <v>0.4074466342999999</v>
       </c>
       <c r="P2">
-        <v>1.74231</v>
+        <v>1.7370093357</v>
       </c>
       <c r="Q2">
-        <v>2.42131</v>
+        <v>2.4160093357</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09055410850237572</v>
+        <v>0.09092027848103154</v>
       </c>
       <c r="T2">
-        <v>0.8723408754896529</v>
+        <v>0.8794782099254774</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>328.6965371491268</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09041850569622123</v>
+        <v>0.0902829028900667</v>
       </c>
       <c r="C3">
-        <v>12.86318866257173</v>
+        <v>12.7418881421846</v>
       </c>
       <c r="D3">
-        <v>11.64328866257173</v>
+        <v>11.6520881421846</v>
       </c>
       <c r="E3">
-        <v>-1.7799</v>
+        <v>-1.6498</v>
       </c>
       <c r="F3">
-        <v>0.1301</v>
+        <v>0.2602</v>
       </c>
       <c r="G3">
         <v>1.35</v>
@@ -1533,28 +1533,28 @@
         <v>2.151</v>
       </c>
       <c r="M3">
-        <v>0.006544029999999999</v>
+        <v>0.01308806</v>
       </c>
       <c r="N3">
-        <v>2.14445597</v>
+        <v>2.13791194</v>
       </c>
       <c r="O3">
-        <v>0.4074466342999999</v>
+        <v>0.4062032686</v>
       </c>
       <c r="P3">
-        <v>1.7370093357</v>
+        <v>1.7317086714</v>
       </c>
       <c r="Q3">
-        <v>2.4160093357</v>
+        <v>2.4107086714</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09092027848103154</v>
+        <v>0.09129392131639459</v>
       </c>
       <c r="T3">
-        <v>0.8794782099254774</v>
+        <v>0.8867612042477472</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>328.6965371491268</v>
+        <v>164.3482685745634</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0902829028900667</v>
+        <v>0.09014730008391218</v>
       </c>
       <c r="C4">
-        <v>12.7418881421846</v>
+        <v>12.62060093236749</v>
       </c>
       <c r="D4">
-        <v>11.6520881421846</v>
+        <v>11.66090093236749</v>
       </c>
       <c r="E4">
-        <v>-1.6498</v>
+        <v>-1.5197</v>
       </c>
       <c r="F4">
-        <v>0.2602</v>
+        <v>0.3903</v>
       </c>
       <c r="G4">
         <v>1.35</v>
@@ -1615,28 +1615,28 @@
         <v>2.151</v>
       </c>
       <c r="M4">
-        <v>0.01308806</v>
+        <v>0.01963209</v>
       </c>
       <c r="N4">
-        <v>2.13791194</v>
+        <v>2.13136791</v>
       </c>
       <c r="O4">
-        <v>0.4062032686</v>
+        <v>0.4049599028999999</v>
       </c>
       <c r="P4">
-        <v>1.7317086714</v>
+        <v>1.7264080071</v>
       </c>
       <c r="Q4">
-        <v>2.4107086714</v>
+        <v>2.4054080071</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09129392131639459</v>
+        <v>0.09167526812774451</v>
       </c>
       <c r="T4">
-        <v>0.8867612042477472</v>
+        <v>0.894194363401404</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>164.3482685745634</v>
+        <v>109.5655123830423</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09014730008391218</v>
+        <v>0.09001169727775768</v>
       </c>
       <c r="C5">
-        <v>12.62060093236749</v>
+        <v>12.4993270633447</v>
       </c>
       <c r="D5">
-        <v>11.66090093236749</v>
+        <v>11.6697270633447</v>
       </c>
       <c r="E5">
-        <v>-1.5197</v>
+        <v>-1.3896</v>
       </c>
       <c r="F5">
-        <v>0.3903</v>
+        <v>0.5204</v>
       </c>
       <c r="G5">
         <v>1.35</v>
@@ -1697,28 +1697,28 @@
         <v>2.151</v>
       </c>
       <c r="M5">
-        <v>0.01963209</v>
+        <v>0.02617612</v>
       </c>
       <c r="N5">
-        <v>2.13136791</v>
+        <v>2.12482388</v>
       </c>
       <c r="O5">
-        <v>0.4049599028999999</v>
+        <v>0.4037165371999999</v>
       </c>
       <c r="P5">
-        <v>1.7264080071</v>
+        <v>1.7211073428</v>
       </c>
       <c r="Q5">
-        <v>2.4054080071</v>
+        <v>2.4001073428</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09167526812774451</v>
+        <v>0.09206455966433091</v>
       </c>
       <c r="T5">
-        <v>0.894194363401404</v>
+        <v>0.9017823800374286</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>109.5655123830423</v>
+        <v>82.17413428728169</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09001169727775768</v>
+        <v>0.08987609447160315</v>
       </c>
       <c r="C6">
-        <v>12.4993270633447</v>
+        <v>12.37806656543209</v>
       </c>
       <c r="D6">
-        <v>11.6697270633447</v>
+        <v>11.67856656543209</v>
       </c>
       <c r="E6">
-        <v>-1.3896</v>
+        <v>-1.2595</v>
       </c>
       <c r="F6">
-        <v>0.5204</v>
+        <v>0.6505000000000001</v>
       </c>
       <c r="G6">
         <v>1.35</v>
@@ -1779,28 +1779,28 @@
         <v>2.151</v>
       </c>
       <c r="M6">
-        <v>0.02617612</v>
+        <v>0.03272015</v>
       </c>
       <c r="N6">
-        <v>2.12482388</v>
+        <v>2.11827985</v>
       </c>
       <c r="O6">
-        <v>0.4037165371999999</v>
+        <v>0.4024731715</v>
       </c>
       <c r="P6">
-        <v>1.7211073428</v>
+        <v>1.7158066785</v>
       </c>
       <c r="Q6">
-        <v>2.4001073428</v>
+        <v>2.3948066785</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09206455966433091</v>
+        <v>0.09246204681221384</v>
       </c>
       <c r="T6">
-        <v>0.9017823800374286</v>
+        <v>0.9095301443921064</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>82.17413428728169</v>
+        <v>65.73930742982535</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08987609447160315</v>
+        <v>0.08974049166544865</v>
       </c>
       <c r="C7">
-        <v>12.37806656543209</v>
+        <v>12.25681946903746</v>
       </c>
       <c r="D7">
-        <v>11.67856656543209</v>
+        <v>11.68741946903746</v>
       </c>
       <c r="E7">
-        <v>-1.2595</v>
+        <v>-1.1294</v>
       </c>
       <c r="F7">
-        <v>0.6505000000000001</v>
+        <v>0.7806000000000001</v>
       </c>
       <c r="G7">
         <v>1.35</v>
@@ -1861,28 +1861,28 @@
         <v>2.151</v>
       </c>
       <c r="M7">
-        <v>0.03272015</v>
+        <v>0.03926418</v>
       </c>
       <c r="N7">
-        <v>2.11827985</v>
+        <v>2.11173582</v>
       </c>
       <c r="O7">
-        <v>0.4024731715</v>
+        <v>0.4012298058</v>
       </c>
       <c r="P7">
-        <v>1.7158066785</v>
+        <v>1.7105060142</v>
       </c>
       <c r="Q7">
-        <v>2.3948066785</v>
+        <v>2.3895060142</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09246204681221384</v>
+        <v>0.09286799113345601</v>
       </c>
       <c r="T7">
-        <v>0.9095301443921064</v>
+        <v>0.9174427547968838</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>65.73930742982535</v>
+        <v>54.78275619152112</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08974049166544865</v>
+        <v>0.08960488885929414</v>
       </c>
       <c r="C8">
-        <v>12.25681946903746</v>
+        <v>12.13558580466087</v>
       </c>
       <c r="D8">
-        <v>11.68741946903746</v>
+        <v>11.69628580466087</v>
       </c>
       <c r="E8">
-        <v>-1.1294</v>
+        <v>-0.9993000000000001</v>
       </c>
       <c r="F8">
-        <v>0.7806</v>
+        <v>0.9106999999999998</v>
       </c>
       <c r="G8">
         <v>1.35</v>
@@ -1943,28 +1943,28 @@
         <v>2.151</v>
       </c>
       <c r="M8">
-        <v>0.03926418</v>
+        <v>0.04580820999999999</v>
       </c>
       <c r="N8">
-        <v>2.11173582</v>
+        <v>2.10519179</v>
       </c>
       <c r="O8">
-        <v>0.4012298058</v>
+        <v>0.3999864401</v>
       </c>
       <c r="P8">
-        <v>1.7105060142</v>
+        <v>1.7052053499</v>
       </c>
       <c r="Q8">
-        <v>2.3895060142</v>
+        <v>2.3842053499</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09286799113345601</v>
+        <v>0.09328266544010122</v>
       </c>
       <c r="T8">
-        <v>0.9174427547968838</v>
+        <v>0.9255255288662801</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>54.78275619152113</v>
+        <v>46.95664816416097</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08960488885929413</v>
+        <v>0.08946928605313963</v>
       </c>
       <c r="C9">
-        <v>12.13558580466087</v>
+        <v>12.01436560289502</v>
       </c>
       <c r="D9">
-        <v>11.69628580466087</v>
+        <v>11.70516560289502</v>
       </c>
       <c r="E9">
-        <v>-0.9992999999999999</v>
+        <v>-0.8692</v>
       </c>
       <c r="F9">
-        <v>0.9107000000000001</v>
+        <v>1.0408</v>
       </c>
       <c r="G9">
         <v>1.35</v>
@@ -2025,28 +2025,28 @@
         <v>2.151</v>
       </c>
       <c r="M9">
-        <v>0.04580821</v>
+        <v>0.05235223999999999</v>
       </c>
       <c r="N9">
-        <v>2.10519179</v>
+        <v>2.09864776</v>
       </c>
       <c r="O9">
-        <v>0.3999864401</v>
+        <v>0.3987430744</v>
       </c>
       <c r="P9">
-        <v>1.7052053499</v>
+        <v>1.6999046856</v>
       </c>
       <c r="Q9">
-        <v>2.3842053499</v>
+        <v>2.3789046856</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09328266544010122</v>
+        <v>0.09370635440558654</v>
       </c>
       <c r="T9">
-        <v>0.9255255288662801</v>
+        <v>0.9337840154154459</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>46.95664816416096</v>
+        <v>41.08706714364085</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08946928605313963</v>
+        <v>0.08933368324698511</v>
       </c>
       <c r="C10">
-        <v>12.01436560289502</v>
+        <v>11.89315889442557</v>
       </c>
       <c r="D10">
-        <v>11.70516560289502</v>
+        <v>11.71405889442557</v>
       </c>
       <c r="E10">
-        <v>-0.8692</v>
+        <v>-0.7391000000000001</v>
       </c>
       <c r="F10">
-        <v>1.0408</v>
+        <v>1.1709</v>
       </c>
       <c r="G10">
         <v>1.35</v>
@@ -2107,28 +2107,28 @@
         <v>2.151</v>
       </c>
       <c r="M10">
-        <v>0.05235223999999999</v>
+        <v>0.05889626999999999</v>
       </c>
       <c r="N10">
-        <v>2.09864776</v>
+        <v>2.09210373</v>
       </c>
       <c r="O10">
-        <v>0.3987430744</v>
+        <v>0.3974997087</v>
       </c>
       <c r="P10">
-        <v>1.6999046856</v>
+        <v>1.6946040213</v>
       </c>
       <c r="Q10">
-        <v>2.3789046856</v>
+        <v>2.3736040213</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09370635440558654</v>
+        <v>0.09413935521646714</v>
       </c>
       <c r="T10">
-        <v>0.9337840154154459</v>
+        <v>0.9422240071634942</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>41.08706714364085</v>
+        <v>36.52183746101409</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08933368324698511</v>
+        <v>0.08919808044083059</v>
       </c>
       <c r="C11">
-        <v>11.89315889442557</v>
+        <v>11.7719657100315</v>
       </c>
       <c r="D11">
-        <v>11.71405889442557</v>
+        <v>11.7229657100315</v>
       </c>
       <c r="E11">
-        <v>-0.7391000000000001</v>
+        <v>-0.609</v>
       </c>
       <c r="F11">
-        <v>1.1709</v>
+        <v>1.301</v>
       </c>
       <c r="G11">
         <v>1.35</v>
@@ -2189,28 +2189,28 @@
         <v>2.151</v>
       </c>
       <c r="M11">
-        <v>0.05889626999999999</v>
+        <v>0.06544029999999999</v>
       </c>
       <c r="N11">
-        <v>2.09210373</v>
+        <v>2.0855597</v>
       </c>
       <c r="O11">
-        <v>0.3974997087</v>
+        <v>0.396256343</v>
       </c>
       <c r="P11">
-        <v>1.6946040213</v>
+        <v>1.689303357</v>
       </c>
       <c r="Q11">
-        <v>2.3736040213</v>
+        <v>2.368303357</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09413935521646714</v>
+        <v>0.09458197826758954</v>
       </c>
       <c r="T11">
-        <v>0.9422240071634942</v>
+        <v>0.9508515542837217</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>36.52183746101409</v>
+        <v>32.86965371491267</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08919808044083059</v>
+        <v>0.08906247763467608</v>
       </c>
       <c r="C12">
-        <v>11.7719657100315</v>
+        <v>11.6507860805855</v>
       </c>
       <c r="D12">
-        <v>11.7229657100315</v>
+        <v>11.7318860805855</v>
       </c>
       <c r="E12">
-        <v>-0.6089999999999998</v>
+        <v>-0.4788999999999999</v>
       </c>
       <c r="F12">
-        <v>1.301</v>
+        <v>1.4311</v>
       </c>
       <c r="G12">
         <v>1.35</v>
@@ -2271,28 +2271,28 @@
         <v>2.151</v>
       </c>
       <c r="M12">
-        <v>0.06544030000000001</v>
+        <v>0.07198433</v>
       </c>
       <c r="N12">
-        <v>2.0855597</v>
+        <v>2.07901567</v>
       </c>
       <c r="O12">
-        <v>0.396256343</v>
+        <v>0.3950129773</v>
       </c>
       <c r="P12">
-        <v>1.689303357</v>
+        <v>1.6840026927</v>
       </c>
       <c r="Q12">
-        <v>2.368303357</v>
+        <v>2.3630026927</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09458197826758954</v>
+        <v>0.09503454790413042</v>
       </c>
       <c r="T12">
-        <v>0.9508515542837217</v>
+        <v>0.9596729788673248</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>32.86965371491267</v>
+        <v>29.88150337719334</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08906247763467608</v>
+        <v>0.08892687482852155</v>
       </c>
       <c r="C13">
-        <v>11.6507860805855</v>
+        <v>11.52962003705427</v>
       </c>
       <c r="D13">
-        <v>11.7318860805855</v>
+        <v>11.74082003705427</v>
       </c>
       <c r="E13">
-        <v>-0.4788999999999999</v>
+        <v>-0.3488</v>
       </c>
       <c r="F13">
-        <v>1.4311</v>
+        <v>1.5612</v>
       </c>
       <c r="G13">
         <v>1.35</v>
@@ -2353,28 +2353,28 @@
         <v>2.151</v>
       </c>
       <c r="M13">
-        <v>0.07198433</v>
+        <v>0.07852835999999999</v>
       </c>
       <c r="N13">
-        <v>2.07901567</v>
+        <v>2.07247164</v>
       </c>
       <c r="O13">
-        <v>0.3950129773</v>
+        <v>0.3937696116</v>
       </c>
       <c r="P13">
-        <v>1.6840026927</v>
+        <v>1.6787020284</v>
       </c>
       <c r="Q13">
-        <v>2.3630026927</v>
+        <v>2.3577020284</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09503454790413042</v>
+        <v>0.09549740321422903</v>
       </c>
       <c r="T13">
-        <v>0.9596729788673248</v>
+        <v>0.9686948903732826</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>29.88150337719334</v>
+        <v>27.39137809576057</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08892687482852155</v>
+        <v>0.08879127202236704</v>
       </c>
       <c r="C14">
-        <v>11.52962003705427</v>
+        <v>11.40846761049892</v>
       </c>
       <c r="D14">
-        <v>11.74082003705427</v>
+        <v>11.74976761049892</v>
       </c>
       <c r="E14">
-        <v>-0.3488</v>
+        <v>-0.2186999999999999</v>
       </c>
       <c r="F14">
-        <v>1.5612</v>
+        <v>1.6913</v>
       </c>
       <c r="G14">
         <v>1.35</v>
@@ -2435,28 +2435,28 @@
         <v>2.151</v>
       </c>
       <c r="M14">
-        <v>0.07852835999999999</v>
+        <v>0.08507239</v>
       </c>
       <c r="N14">
-        <v>2.07247164</v>
+        <v>2.06592761</v>
       </c>
       <c r="O14">
-        <v>0.3937696116</v>
+        <v>0.3925262459</v>
       </c>
       <c r="P14">
-        <v>1.6787020284</v>
+        <v>1.6734013641</v>
       </c>
       <c r="Q14">
-        <v>2.3577020284</v>
+        <v>2.352401364099999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09549740321422903</v>
+        <v>0.09597089887628396</v>
       </c>
       <c r="T14">
-        <v>0.9686948903732826</v>
+        <v>0.9779242021437454</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>27.39137809576057</v>
+        <v>25.28434901147128</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08879127202236704</v>
+        <v>0.08865566921621254</v>
       </c>
       <c r="C15">
-        <v>11.40846761049892</v>
+        <v>11.28732883207533</v>
       </c>
       <c r="D15">
-        <v>11.74976761049892</v>
+        <v>11.75872883207533</v>
       </c>
       <c r="E15">
-        <v>-0.2186999999999999</v>
+        <v>-0.08859999999999979</v>
       </c>
       <c r="F15">
-        <v>1.6913</v>
+        <v>1.8214</v>
       </c>
       <c r="G15">
         <v>1.35</v>
@@ -2517,28 +2517,28 @@
         <v>2.151</v>
       </c>
       <c r="M15">
-        <v>0.08507239</v>
+        <v>0.09161642</v>
       </c>
       <c r="N15">
-        <v>2.06592761</v>
+        <v>2.05938358</v>
       </c>
       <c r="O15">
-        <v>0.3925262459</v>
+        <v>0.3912828802</v>
       </c>
       <c r="P15">
-        <v>1.6734013641</v>
+        <v>1.6681006998</v>
       </c>
       <c r="Q15">
-        <v>2.352401364099999</v>
+        <v>2.3471006998</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09597089887628396</v>
+        <v>0.09645540606536342</v>
       </c>
       <c r="T15">
-        <v>0.9779242021437454</v>
+        <v>0.9873681490716607</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>25.28434901147128</v>
+        <v>23.47832408208048</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08865566921621254</v>
+        <v>0.08852006641005802</v>
       </c>
       <c r="C16">
-        <v>11.28732883207533</v>
+        <v>11.16620373303448</v>
       </c>
       <c r="D16">
-        <v>11.75872883207533</v>
+        <v>11.76770373303448</v>
       </c>
       <c r="E16">
-        <v>-0.08859999999999979</v>
+        <v>0.04150000000000031</v>
       </c>
       <c r="F16">
-        <v>1.8214</v>
+        <v>1.9515</v>
       </c>
       <c r="G16">
         <v>1.35</v>
@@ -2599,28 +2599,28 @@
         <v>2.151</v>
       </c>
       <c r="M16">
-        <v>0.09161642</v>
+        <v>0.09816045000000001</v>
       </c>
       <c r="N16">
-        <v>2.05938358</v>
+        <v>2.05283955</v>
       </c>
       <c r="O16">
-        <v>0.3912828802</v>
+        <v>0.3900395145</v>
       </c>
       <c r="P16">
-        <v>1.6681006998</v>
+        <v>1.6628000355</v>
       </c>
       <c r="Q16">
-        <v>2.3471006998</v>
+        <v>2.3418000355</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09645540606536342</v>
+        <v>0.09695131342359767</v>
       </c>
       <c r="T16">
-        <v>0.9873681490716607</v>
+        <v>0.9970343065155269</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>23.47832408208048</v>
+        <v>21.91310247660845</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08852006641005802</v>
+        <v>0.08838446360390351</v>
       </c>
       <c r="C17">
-        <v>11.16620373303448</v>
+        <v>11.04509234472284</v>
       </c>
       <c r="D17">
-        <v>11.76770373303448</v>
+        <v>11.77669234472284</v>
       </c>
       <c r="E17">
-        <v>0.04149999999999987</v>
+        <v>0.1716</v>
       </c>
       <c r="F17">
-        <v>1.9515</v>
+        <v>2.0816</v>
       </c>
       <c r="G17">
         <v>1.35</v>
@@ -2681,28 +2681,28 @@
         <v>2.151</v>
       </c>
       <c r="M17">
-        <v>0.09816044999999998</v>
+        <v>0.10470448</v>
       </c>
       <c r="N17">
-        <v>2.05283955</v>
+        <v>2.04629552</v>
       </c>
       <c r="O17">
-        <v>0.3900395145</v>
+        <v>0.3887961488</v>
       </c>
       <c r="P17">
-        <v>1.6628000355</v>
+        <v>1.6574993712</v>
       </c>
       <c r="Q17">
-        <v>2.3418000355</v>
+        <v>2.3364993712</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09695131342359767</v>
+        <v>0.09745902809988513</v>
       </c>
       <c r="T17">
-        <v>0.9970343065155269</v>
+        <v>1.006930610565199</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.91310247660845</v>
+        <v>20.54353357182042</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08838446360390351</v>
+        <v>0.088248860797749</v>
       </c>
       <c r="C18">
-        <v>11.04509234472284</v>
+        <v>10.92399469858273</v>
       </c>
       <c r="D18">
-        <v>11.77669234472284</v>
+        <v>11.78569469858273</v>
       </c>
       <c r="E18">
-        <v>0.1716</v>
+        <v>0.3017000000000001</v>
       </c>
       <c r="F18">
-        <v>2.0816</v>
+        <v>2.2117</v>
       </c>
       <c r="G18">
         <v>1.35</v>
@@ -2763,28 +2763,28 @@
         <v>2.151</v>
       </c>
       <c r="M18">
-        <v>0.10470448</v>
+        <v>0.11124851</v>
       </c>
       <c r="N18">
-        <v>2.04629552</v>
+        <v>2.03975149</v>
       </c>
       <c r="O18">
-        <v>0.3887961488</v>
+        <v>0.3875527831</v>
       </c>
       <c r="P18">
-        <v>1.6574993712</v>
+        <v>1.6521987069</v>
       </c>
       <c r="Q18">
-        <v>2.3364993712</v>
+        <v>2.3311987069</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09745902809988513</v>
+        <v>0.09797897686475783</v>
       </c>
       <c r="T18">
-        <v>1.006930610565199</v>
+        <v>1.017065379772695</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>20.54353357182042</v>
+        <v>19.33509042053687</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.088248860797749</v>
+        <v>0.08811325799159447</v>
       </c>
       <c r="C19">
-        <v>10.92399469858273</v>
+        <v>10.80291082615269</v>
       </c>
       <c r="D19">
-        <v>11.78569469858273</v>
+        <v>11.79471082615269</v>
       </c>
       <c r="E19">
-        <v>0.3017000000000001</v>
+        <v>0.4318000000000002</v>
       </c>
       <c r="F19">
-        <v>2.2117</v>
+        <v>2.3418</v>
       </c>
       <c r="G19">
         <v>1.35</v>
@@ -2845,28 +2845,28 @@
         <v>2.151</v>
       </c>
       <c r="M19">
-        <v>0.11124851</v>
+        <v>0.11779254</v>
       </c>
       <c r="N19">
-        <v>2.03975149</v>
+        <v>2.03320746</v>
       </c>
       <c r="O19">
-        <v>0.3875527831</v>
+        <v>0.3863094174</v>
       </c>
       <c r="P19">
-        <v>1.6521987069</v>
+        <v>1.6468980426</v>
       </c>
       <c r="Q19">
-        <v>2.3311987069</v>
+        <v>2.3258980426</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09797897686475783</v>
+        <v>0.09851160730682253</v>
       </c>
       <c r="T19">
-        <v>1.017065379772695</v>
+        <v>1.027447338473057</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>19.33509042053687</v>
+        <v>18.26091873050704</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08811325799159449</v>
+        <v>0.08797765518543997</v>
       </c>
       <c r="C20">
-        <v>10.80291082615268</v>
+        <v>10.68184075906781</v>
       </c>
       <c r="D20">
-        <v>11.79471082615268</v>
+        <v>11.80374075906781</v>
       </c>
       <c r="E20">
-        <v>0.4317999999999997</v>
+        <v>0.5619000000000003</v>
       </c>
       <c r="F20">
-        <v>2.3418</v>
+        <v>2.4719</v>
       </c>
       <c r="G20">
         <v>1.35</v>
@@ -2927,28 +2927,28 @@
         <v>2.151</v>
       </c>
       <c r="M20">
-        <v>0.11779254</v>
+        <v>0.12433657</v>
       </c>
       <c r="N20">
-        <v>2.03320746</v>
+        <v>2.02666343</v>
       </c>
       <c r="O20">
-        <v>0.3863094174</v>
+        <v>0.3850660517</v>
       </c>
       <c r="P20">
-        <v>1.6468980426</v>
+        <v>1.6415973783</v>
       </c>
       <c r="Q20">
-        <v>2.3258980426</v>
+        <v>2.3205973783</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09851160730682253</v>
+        <v>0.09905738911782712</v>
       </c>
       <c r="T20">
-        <v>1.027447338473057</v>
+        <v>1.038085641832687</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>18.26091873050704</v>
+        <v>17.29981774469088</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08797765518543997</v>
+        <v>0.08784205237928545</v>
       </c>
       <c r="C21">
-        <v>10.68184075906781</v>
+        <v>10.56078452906019</v>
       </c>
       <c r="D21">
-        <v>11.80374075906781</v>
+        <v>11.81278452906019</v>
       </c>
       <c r="E21">
-        <v>0.5619000000000003</v>
+        <v>0.6920000000000004</v>
       </c>
       <c r="F21">
-        <v>2.4719</v>
+        <v>2.602</v>
       </c>
       <c r="G21">
         <v>1.35</v>
@@ -3009,28 +3009,28 @@
         <v>2.151</v>
       </c>
       <c r="M21">
-        <v>0.12433657</v>
+        <v>0.1308806</v>
       </c>
       <c r="N21">
-        <v>2.02666343</v>
+        <v>2.0201194</v>
       </c>
       <c r="O21">
-        <v>0.3850660517</v>
+        <v>0.3838226859999999</v>
       </c>
       <c r="P21">
-        <v>1.6415973783</v>
+        <v>1.636296714</v>
       </c>
       <c r="Q21">
-        <v>2.3205973783</v>
+        <v>2.315296714</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09905738911782712</v>
+        <v>0.09961681547410681</v>
       </c>
       <c r="T21">
-        <v>1.038085641832687</v>
+        <v>1.048989902776308</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>17.29981774469088</v>
+        <v>16.43482685745633</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08784205237928545</v>
+        <v>0.08770644957313095</v>
       </c>
       <c r="C22">
-        <v>10.56078452906019</v>
+        <v>10.4397421679592</v>
       </c>
       <c r="D22">
-        <v>11.81278452906019</v>
+        <v>11.8218421679592</v>
       </c>
       <c r="E22">
-        <v>0.6920000000000004</v>
+        <v>0.8221000000000005</v>
       </c>
       <c r="F22">
-        <v>2.602</v>
+        <v>2.7321</v>
       </c>
       <c r="G22">
         <v>1.35</v>
@@ -3091,28 +3091,28 @@
         <v>2.151</v>
       </c>
       <c r="M22">
-        <v>0.1308806</v>
+        <v>0.13742463</v>
       </c>
       <c r="N22">
-        <v>2.0201194</v>
+        <v>2.01357537</v>
       </c>
       <c r="O22">
-        <v>0.3838226859999999</v>
+        <v>0.3825793203</v>
       </c>
       <c r="P22">
-        <v>1.636296714</v>
+        <v>1.6309960497</v>
       </c>
       <c r="Q22">
-        <v>2.315296714</v>
+        <v>2.3099960497</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09961681547410681</v>
+        <v>0.1001904045229506</v>
       </c>
       <c r="T22">
-        <v>1.048989902776308</v>
+        <v>1.060170220959007</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.43482685745633</v>
+        <v>15.65221605472032</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08770644957313095</v>
+        <v>0.08757084676697643</v>
       </c>
       <c r="C23">
-        <v>10.4397421679592</v>
+        <v>10.31871370769194</v>
       </c>
       <c r="D23">
-        <v>11.8218421679592</v>
+        <v>11.83091370769194</v>
       </c>
       <c r="E23">
-        <v>0.8221000000000001</v>
+        <v>0.9522000000000002</v>
       </c>
       <c r="F23">
-        <v>2.7321</v>
+        <v>2.8622</v>
       </c>
       <c r="G23">
         <v>1.35</v>
@@ -3173,28 +3173,28 @@
         <v>2.151</v>
       </c>
       <c r="M23">
-        <v>0.13742463</v>
+        <v>0.14396866</v>
       </c>
       <c r="N23">
-        <v>2.01357537</v>
+        <v>2.00703134</v>
       </c>
       <c r="O23">
-        <v>0.3825793203</v>
+        <v>0.3813359546</v>
       </c>
       <c r="P23">
-        <v>1.6309960497</v>
+        <v>1.6256953854</v>
       </c>
       <c r="Q23">
-        <v>2.3099960497</v>
+        <v>2.3046953854</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1001904045229506</v>
+        <v>0.1007787009833031</v>
       </c>
       <c r="T23">
-        <v>1.060170220959007</v>
+        <v>1.071637213966904</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.65221605472032</v>
+        <v>14.94075168859667</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08757084676697643</v>
+        <v>0.0874352439608219</v>
       </c>
       <c r="C24">
-        <v>10.31871370769194</v>
+        <v>10.19769918028356</v>
       </c>
       <c r="D24">
-        <v>11.83091370769194</v>
+        <v>11.83999918028356</v>
       </c>
       <c r="E24">
-        <v>0.9522000000000002</v>
+        <v>1.0823</v>
       </c>
       <c r="F24">
-        <v>2.8622</v>
+        <v>2.9923</v>
       </c>
       <c r="G24">
         <v>1.35</v>
@@ -3255,28 +3255,28 @@
         <v>2.151</v>
       </c>
       <c r="M24">
-        <v>0.14396866</v>
+        <v>0.15051269</v>
       </c>
       <c r="N24">
-        <v>2.00703134</v>
+        <v>2.00048731</v>
       </c>
       <c r="O24">
-        <v>0.3813359546</v>
+        <v>0.3800925888999999</v>
       </c>
       <c r="P24">
-        <v>1.6256953854</v>
+        <v>1.6203947211</v>
       </c>
       <c r="Q24">
-        <v>2.3046953854</v>
+        <v>2.2993947211</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1007787009833031</v>
+        <v>0.1013822778711973</v>
       </c>
       <c r="T24">
-        <v>1.071637213966904</v>
+        <v>1.083402050949033</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.94075168859667</v>
+        <v>14.29115378909246</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0874352439608219</v>
+        <v>0.0872996411546674</v>
       </c>
       <c r="C25">
-        <v>10.19769918028356</v>
+        <v>10.07669861785769</v>
       </c>
       <c r="D25">
-        <v>11.83999918028356</v>
+        <v>11.84909861785769</v>
       </c>
       <c r="E25">
-        <v>1.0823</v>
+        <v>1.2124</v>
       </c>
       <c r="F25">
-        <v>2.9923</v>
+        <v>3.1224</v>
       </c>
       <c r="G25">
         <v>1.35</v>
@@ -3337,28 +3337,28 @@
         <v>2.151</v>
       </c>
       <c r="M25">
-        <v>0.15051269</v>
+        <v>0.15705672</v>
       </c>
       <c r="N25">
-        <v>2.00048731</v>
+        <v>1.99394328</v>
       </c>
       <c r="O25">
-        <v>0.3800925888999999</v>
+        <v>0.3788492232</v>
       </c>
       <c r="P25">
-        <v>1.6203947211</v>
+        <v>1.6150940568</v>
       </c>
       <c r="Q25">
-        <v>2.2993947211</v>
+        <v>2.2940940568</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1013822778711973</v>
+        <v>0.1020017383614045</v>
       </c>
       <c r="T25">
-        <v>1.083402050949033</v>
+        <v>1.095476488904375</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.29115378909246</v>
+        <v>13.69568904788028</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0872996411546674</v>
+        <v>0.08716403834851288</v>
       </c>
       <c r="C26">
-        <v>10.07669861785769</v>
+        <v>9.955712052636757</v>
       </c>
       <c r="D26">
-        <v>11.84909861785769</v>
+        <v>11.85821205263676</v>
       </c>
       <c r="E26">
-        <v>1.2124</v>
+        <v>1.3425</v>
       </c>
       <c r="F26">
-        <v>3.1224</v>
+        <v>3.2525</v>
       </c>
       <c r="G26">
         <v>1.35</v>
@@ -3419,28 +3419,28 @@
         <v>2.151</v>
       </c>
       <c r="M26">
-        <v>0.15705672</v>
+        <v>0.16360075</v>
       </c>
       <c r="N26">
-        <v>1.99394328</v>
+        <v>1.98739925</v>
       </c>
       <c r="O26">
-        <v>0.3788492232</v>
+        <v>0.3776058575</v>
       </c>
       <c r="P26">
-        <v>1.6150940568</v>
+        <v>1.6097933925</v>
       </c>
       <c r="Q26">
-        <v>2.2940940568</v>
+        <v>2.2887933925</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1020017383614045</v>
+        <v>0.1026377177980172</v>
       </c>
       <c r="T26">
-        <v>1.095476488904375</v>
+        <v>1.107872911871859</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>13.69568904788028</v>
+        <v>13.14786148596507</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08716403834851288</v>
+        <v>0.08734433554235838</v>
       </c>
       <c r="C27">
-        <v>9.955712052636757</v>
+        <v>9.813497918324586</v>
       </c>
       <c r="D27">
-        <v>11.85821205263676</v>
+        <v>11.84609791832459</v>
       </c>
       <c r="E27">
-        <v>1.3425</v>
+        <v>1.4726</v>
       </c>
       <c r="F27">
-        <v>3.2525</v>
+        <v>3.3826</v>
       </c>
       <c r="G27">
         <v>1.35</v>
@@ -3501,45 +3501,45 @@
         <v>2.151</v>
       </c>
       <c r="M27">
-        <v>0.16360075</v>
+        <v>0.17521868</v>
       </c>
       <c r="N27">
-        <v>1.98739925</v>
+        <v>1.97578132</v>
       </c>
       <c r="O27">
-        <v>0.3776058575</v>
+        <v>0.3753984507999999</v>
       </c>
       <c r="P27">
-        <v>1.6097933925</v>
+        <v>1.6003828692</v>
       </c>
       <c r="Q27">
-        <v>2.2887933925</v>
+        <v>2.2793828692</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1026377177980172</v>
+        <v>0.1032908858680519</v>
       </c>
       <c r="T27">
-        <v>1.107872911871859</v>
+        <v>1.120604373297925</v>
       </c>
       <c r="U27">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V27">
         <v>0.19</v>
       </c>
       <c r="W27">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y27">
-        <v>13.14786148596507</v>
+        <v>12.27608837139967</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08734433554235838</v>
+        <v>0.08722088273620386</v>
       </c>
       <c r="C28">
-        <v>9.813497918324586</v>
+        <v>9.691690015492943</v>
       </c>
       <c r="D28">
-        <v>11.84609791832459</v>
+        <v>11.85439001549294</v>
       </c>
       <c r="E28">
-        <v>1.4726</v>
+        <v>1.6027</v>
       </c>
       <c r="F28">
-        <v>3.3826</v>
+        <v>3.5127</v>
       </c>
       <c r="G28">
         <v>1.35</v>
@@ -3583,28 +3583,28 @@
         <v>2.151</v>
       </c>
       <c r="M28">
-        <v>0.17521868</v>
+        <v>0.18195786</v>
       </c>
       <c r="N28">
-        <v>1.97578132</v>
+        <v>1.96904214</v>
       </c>
       <c r="O28">
-        <v>0.3753984507999999</v>
+        <v>0.3741180065999999</v>
       </c>
       <c r="P28">
-        <v>1.6003828692</v>
+        <v>1.5949241334</v>
       </c>
       <c r="Q28">
-        <v>2.2793828692</v>
+        <v>2.2739241334</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1032908858680519</v>
+        <v>0.1039619489537039</v>
       </c>
       <c r="T28">
-        <v>1.120604373297925</v>
+        <v>1.133684641886348</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>12.27608837139967</v>
+        <v>11.8214184317182</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08722088273620386</v>
+        <v>0.08709742993004933</v>
       </c>
       <c r="C29">
-        <v>9.691690015492943</v>
+        <v>9.569893729489031</v>
       </c>
       <c r="D29">
-        <v>11.85439001549294</v>
+        <v>11.86269372948903</v>
       </c>
       <c r="E29">
-        <v>1.6027</v>
+        <v>1.7328</v>
       </c>
       <c r="F29">
-        <v>3.5127</v>
+        <v>3.6428</v>
       </c>
       <c r="G29">
         <v>1.35</v>
@@ -3665,28 +3665,28 @@
         <v>2.151</v>
       </c>
       <c r="M29">
-        <v>0.18195786</v>
+        <v>0.18869704</v>
       </c>
       <c r="N29">
-        <v>1.96904214</v>
+        <v>1.96230296</v>
       </c>
       <c r="O29">
-        <v>0.3741180065999999</v>
+        <v>0.3728375623999999</v>
       </c>
       <c r="P29">
-        <v>1.5949241334</v>
+        <v>1.5894653976</v>
       </c>
       <c r="Q29">
-        <v>2.2739241334</v>
+        <v>2.2684653976</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1039619489537039</v>
+        <v>0.1046516526806241</v>
       </c>
       <c r="T29">
-        <v>1.133684641886348</v>
+        <v>1.147128251268893</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.8214184317182</v>
+        <v>11.39922491629969</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08709742993004933</v>
+        <v>0.08697397712389482</v>
       </c>
       <c r="C30">
-        <v>9.569893729489031</v>
+        <v>9.448109084741878</v>
       </c>
       <c r="D30">
-        <v>11.86269372948903</v>
+        <v>11.87100908474188</v>
       </c>
       <c r="E30">
-        <v>1.7328</v>
+        <v>1.8629</v>
       </c>
       <c r="F30">
-        <v>3.6428</v>
+        <v>3.7729</v>
       </c>
       <c r="G30">
         <v>1.35</v>
@@ -3747,28 +3747,28 @@
         <v>2.151</v>
       </c>
       <c r="M30">
-        <v>0.18869704</v>
+        <v>0.19543622</v>
       </c>
       <c r="N30">
-        <v>1.96230296</v>
+        <v>1.95556378</v>
       </c>
       <c r="O30">
-        <v>0.3728375623999999</v>
+        <v>0.3715571182</v>
       </c>
       <c r="P30">
-        <v>1.5894653976</v>
+        <v>1.5840066618</v>
       </c>
       <c r="Q30">
-        <v>2.2684653976</v>
+        <v>2.2630066618</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1046516526806241</v>
+        <v>0.105360784681542</v>
       </c>
       <c r="T30">
-        <v>1.147128251268893</v>
+        <v>1.160950553873483</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.39922491629969</v>
+        <v>11.00614819504798</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08697397712389482</v>
+        <v>0.0868505243177403</v>
       </c>
       <c r="C31">
-        <v>9.448109084741878</v>
+        <v>9.326336105749064</v>
       </c>
       <c r="D31">
-        <v>11.87100908474188</v>
+        <v>11.87933610574906</v>
       </c>
       <c r="E31">
-        <v>1.8629</v>
+        <v>1.993</v>
       </c>
       <c r="F31">
-        <v>3.772899999999999</v>
+        <v>3.903</v>
       </c>
       <c r="G31">
         <v>1.35</v>
@@ -3829,28 +3829,28 @@
         <v>2.151</v>
       </c>
       <c r="M31">
-        <v>0.19543622</v>
+        <v>0.2021754</v>
       </c>
       <c r="N31">
-        <v>1.95556378</v>
+        <v>1.9488246</v>
       </c>
       <c r="O31">
-        <v>0.3715571182</v>
+        <v>0.370276674</v>
       </c>
       <c r="P31">
-        <v>1.5840066618</v>
+        <v>1.578547926</v>
       </c>
       <c r="Q31">
-        <v>2.2630066618</v>
+        <v>2.257547926</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.105360784681542</v>
+        <v>0.1060901775967719</v>
       </c>
       <c r="T31">
-        <v>1.160950553873483</v>
+        <v>1.175167779409632</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.00614819504798</v>
+        <v>10.63927658854638</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0868505243177403</v>
+        <v>0.08672707151158579</v>
       </c>
       <c r="C32">
-        <v>9.326336105749064</v>
+        <v>9.204574817076953</v>
       </c>
       <c r="D32">
-        <v>11.87933610574906</v>
+        <v>11.88767481707695</v>
       </c>
       <c r="E32">
-        <v>1.993</v>
+        <v>2.1231</v>
       </c>
       <c r="F32">
-        <v>3.903</v>
+        <v>4.0331</v>
       </c>
       <c r="G32">
         <v>1.35</v>
@@ -3911,28 +3911,28 @@
         <v>2.151</v>
       </c>
       <c r="M32">
-        <v>0.2021754</v>
+        <v>0.20891458</v>
       </c>
       <c r="N32">
-        <v>1.9488246</v>
+        <v>1.94208542</v>
       </c>
       <c r="O32">
-        <v>0.370276674</v>
+        <v>0.3689962298</v>
       </c>
       <c r="P32">
-        <v>1.578547926</v>
+        <v>1.5730891902</v>
       </c>
       <c r="Q32">
-        <v>2.257547926</v>
+        <v>2.2520891902</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1060901775967719</v>
+        <v>0.1068407123356316</v>
       </c>
       <c r="T32">
-        <v>1.175167779409632</v>
+        <v>1.189797098439583</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.63927658854638</v>
+        <v>10.29607411794811</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08672707151158579</v>
+        <v>0.08660361870543129</v>
       </c>
       <c r="C33">
-        <v>9.204574817076953</v>
+        <v>9.082825243360933</v>
       </c>
       <c r="D33">
-        <v>11.88767481707695</v>
+        <v>11.89602524336093</v>
       </c>
       <c r="E33">
-        <v>2.1231</v>
+        <v>2.2532</v>
       </c>
       <c r="F33">
-        <v>4.0331</v>
+        <v>4.1632</v>
       </c>
       <c r="G33">
         <v>1.35</v>
@@ -3993,28 +3993,28 @@
         <v>2.151</v>
       </c>
       <c r="M33">
-        <v>0.20891458</v>
+        <v>0.21565376</v>
       </c>
       <c r="N33">
-        <v>1.94208542</v>
+        <v>1.93534624</v>
       </c>
       <c r="O33">
-        <v>0.3689962298</v>
+        <v>0.3677157856</v>
       </c>
       <c r="P33">
-        <v>1.5730891902</v>
+        <v>1.5676304544</v>
       </c>
       <c r="Q33">
-        <v>2.2520891902</v>
+        <v>2.2466304544</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1068407123356316</v>
+        <v>0.1076133216256343</v>
       </c>
       <c r="T33">
-        <v>1.189797098439583</v>
+        <v>1.20485669155865</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.29607411794811</v>
+        <v>9.974321801762233</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08660361870543129</v>
+        <v>0.08693457589927678</v>
       </c>
       <c r="C34">
-        <v>9.082825243360933</v>
+        <v>8.930365469949269</v>
       </c>
       <c r="D34">
-        <v>11.89602524336093</v>
+        <v>11.87366546994927</v>
       </c>
       <c r="E34">
-        <v>2.2532</v>
+        <v>2.3833</v>
       </c>
       <c r="F34">
-        <v>4.1632</v>
+        <v>4.2933</v>
       </c>
       <c r="G34">
         <v>1.35</v>
@@ -4075,45 +4075,45 @@
         <v>2.151</v>
       </c>
       <c r="M34">
-        <v>0.21565376</v>
+        <v>0.22969155</v>
       </c>
       <c r="N34">
-        <v>1.93534624</v>
+        <v>1.92130845</v>
       </c>
       <c r="O34">
-        <v>0.3677157856</v>
+        <v>0.3650486055</v>
       </c>
       <c r="P34">
-        <v>1.5676304544</v>
+        <v>1.5562598445</v>
       </c>
       <c r="Q34">
-        <v>2.2466304544</v>
+        <v>2.2352598445</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1076133216256343</v>
+        <v>0.1084089938795176</v>
       </c>
       <c r="T34">
-        <v>1.20485669155865</v>
+        <v>1.220365824770824</v>
       </c>
       <c r="U34">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V34">
         <v>0.19</v>
       </c>
       <c r="W34">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>9.974321801762233</v>
+        <v>9.364732834098596</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08693457589927678</v>
+        <v>0.08682489309312226</v>
       </c>
       <c r="C35">
-        <v>8.930365469949269</v>
+        <v>8.807666423396874</v>
       </c>
       <c r="D35">
-        <v>11.87366546994927</v>
+        <v>11.88106642339687</v>
       </c>
       <c r="E35">
-        <v>2.3833</v>
+        <v>2.5134</v>
       </c>
       <c r="F35">
-        <v>4.2933</v>
+        <v>4.4234</v>
       </c>
       <c r="G35">
         <v>1.35</v>
@@ -4157,28 +4157,28 @@
         <v>2.151</v>
       </c>
       <c r="M35">
-        <v>0.22969155</v>
+        <v>0.2366519</v>
       </c>
       <c r="N35">
-        <v>1.92130845</v>
+        <v>1.9143481</v>
       </c>
       <c r="O35">
-        <v>0.3650486055</v>
+        <v>0.3637261389999999</v>
       </c>
       <c r="P35">
-        <v>1.5562598445</v>
+        <v>1.550621961</v>
       </c>
       <c r="Q35">
-        <v>2.2352598445</v>
+        <v>2.229621961</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1084089938795176</v>
+        <v>0.1092287774138216</v>
       </c>
       <c r="T35">
-        <v>1.220365824770824</v>
+        <v>1.236344931716699</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.364732834098596</v>
+        <v>9.089299515448639</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08682489309312226</v>
+        <v>0.08671521028696774</v>
       </c>
       <c r="C36">
-        <v>8.807666423396874</v>
+        <v>8.684976608749235</v>
       </c>
       <c r="D36">
-        <v>11.88106642339687</v>
+        <v>11.88847660874923</v>
       </c>
       <c r="E36">
-        <v>2.5134</v>
+        <v>2.6435</v>
       </c>
       <c r="F36">
-        <v>4.4234</v>
+        <v>4.553500000000001</v>
       </c>
       <c r="G36">
         <v>1.35</v>
@@ -4239,28 +4239,28 @@
         <v>2.151</v>
       </c>
       <c r="M36">
-        <v>0.2366519</v>
+        <v>0.24361225</v>
       </c>
       <c r="N36">
-        <v>1.9143481</v>
+        <v>1.90738775</v>
       </c>
       <c r="O36">
-        <v>0.3637261389999999</v>
+        <v>0.3624036725</v>
       </c>
       <c r="P36">
-        <v>1.550621961</v>
+        <v>1.5449840775</v>
       </c>
       <c r="Q36">
-        <v>2.229621961</v>
+        <v>2.2239840775</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1092287774138216</v>
+        <v>0.1100737850568735</v>
       </c>
       <c r="T36">
-        <v>1.236344931716699</v>
+        <v>1.252815703491678</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>9.089299515448639</v>
+        <v>8.829605243578676</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08671521028696774</v>
+        <v>0.08660552748081324</v>
       </c>
       <c r="C37">
-        <v>8.684976608749235</v>
+        <v>8.562296043290869</v>
       </c>
       <c r="D37">
-        <v>11.88847660874923</v>
+        <v>11.89589604329087</v>
       </c>
       <c r="E37">
-        <v>2.6435</v>
+        <v>2.7736</v>
       </c>
       <c r="F37">
-        <v>4.553500000000001</v>
+        <v>4.6836</v>
       </c>
       <c r="G37">
         <v>1.35</v>
@@ -4321,28 +4321,28 @@
         <v>2.151</v>
       </c>
       <c r="M37">
-        <v>0.24361225</v>
+        <v>0.2505726</v>
       </c>
       <c r="N37">
-        <v>1.90738775</v>
+        <v>1.9004274</v>
       </c>
       <c r="O37">
-        <v>0.3624036725</v>
+        <v>0.361081206</v>
       </c>
       <c r="P37">
-        <v>1.5449840775</v>
+        <v>1.539346194</v>
       </c>
       <c r="Q37">
-        <v>2.2239840775</v>
+        <v>2.218346194</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1100737850568735</v>
+        <v>0.1109451991887707</v>
       </c>
       <c r="T37">
-        <v>1.252815703491678</v>
+        <v>1.269801186884626</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.829605243578676</v>
+        <v>8.584338431257049</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08660552748081322</v>
+        <v>0.08649584467465872</v>
       </c>
       <c r="C38">
-        <v>8.562296043290871</v>
+        <v>8.439624744349466</v>
       </c>
       <c r="D38">
-        <v>11.89589604329087</v>
+        <v>11.90332474434947</v>
       </c>
       <c r="E38">
-        <v>2.773599999999999</v>
+        <v>2.9037</v>
       </c>
       <c r="F38">
-        <v>4.683599999999999</v>
+        <v>4.8137</v>
       </c>
       <c r="G38">
         <v>1.35</v>
@@ -4403,28 +4403,28 @@
         <v>2.151</v>
       </c>
       <c r="M38">
-        <v>0.2505726</v>
+        <v>0.25753295</v>
       </c>
       <c r="N38">
-        <v>1.9004274</v>
+        <v>1.89346705</v>
       </c>
       <c r="O38">
-        <v>0.361081206</v>
+        <v>0.3597587395</v>
       </c>
       <c r="P38">
-        <v>1.539346194</v>
+        <v>1.5337083105</v>
       </c>
       <c r="Q38">
-        <v>2.218346194</v>
+        <v>2.2127083105</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1109451991887707</v>
+        <v>0.111844277261363</v>
       </c>
       <c r="T38">
-        <v>1.269801186884626</v>
+        <v>1.287325891972588</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.584338431257049</v>
+        <v>8.352329284466318</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08649584467465872</v>
+        <v>0.08638616186850422</v>
       </c>
       <c r="C39">
-        <v>8.439624744349466</v>
+        <v>8.316962729296023</v>
       </c>
       <c r="D39">
-        <v>11.90332474434947</v>
+        <v>11.91076272929602</v>
       </c>
       <c r="E39">
-        <v>2.9037</v>
+        <v>3.0338</v>
       </c>
       <c r="F39">
-        <v>4.8137</v>
+        <v>4.9438</v>
       </c>
       <c r="G39">
         <v>1.35</v>
@@ -4485,28 +4485,28 @@
         <v>2.151</v>
       </c>
       <c r="M39">
-        <v>0.25753295</v>
+        <v>0.2644933</v>
       </c>
       <c r="N39">
-        <v>1.89346705</v>
+        <v>1.8865067</v>
       </c>
       <c r="O39">
-        <v>0.3597587395</v>
+        <v>0.358436273</v>
       </c>
       <c r="P39">
-        <v>1.5337083105</v>
+        <v>1.528070427</v>
       </c>
       <c r="Q39">
-        <v>2.2127083105</v>
+        <v>2.207070427</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.111844277261363</v>
+        <v>0.1127723578524261</v>
       </c>
       <c r="T39">
-        <v>1.287325891972588</v>
+        <v>1.305415910127903</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.352329284466318</v>
+        <v>8.132531145401412</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08638616186850422</v>
+        <v>0.0862764790623497</v>
       </c>
       <c r="C40">
-        <v>8.316962729296023</v>
+        <v>8.194310015544989</v>
       </c>
       <c r="D40">
-        <v>11.91076272929602</v>
+        <v>11.91821001554499</v>
       </c>
       <c r="E40">
-        <v>3.0338</v>
+        <v>3.1639</v>
       </c>
       <c r="F40">
-        <v>4.9438</v>
+        <v>5.0739</v>
       </c>
       <c r="G40">
         <v>1.35</v>
@@ -4567,28 +4567,28 @@
         <v>2.151</v>
       </c>
       <c r="M40">
-        <v>0.2644933</v>
+        <v>0.27145365</v>
       </c>
       <c r="N40">
-        <v>1.8865067</v>
+        <v>1.87954635</v>
       </c>
       <c r="O40">
-        <v>0.358436273</v>
+        <v>0.3571138065</v>
       </c>
       <c r="P40">
-        <v>1.528070427</v>
+        <v>1.5224325435</v>
       </c>
       <c r="Q40">
-        <v>2.207070427</v>
+        <v>2.2014325435</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1127723578524261</v>
+        <v>0.1137308673153274</v>
       </c>
       <c r="T40">
-        <v>1.305415910127903</v>
+        <v>1.324099043632573</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.132531145401412</v>
+        <v>7.924004705775737</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0862764790623497</v>
+        <v>0.08616679625619517</v>
       </c>
       <c r="C41">
-        <v>8.194310015544989</v>
+        <v>8.071666620554383</v>
       </c>
       <c r="D41">
-        <v>11.91821001554499</v>
+        <v>11.92566662055438</v>
       </c>
       <c r="E41">
-        <v>3.1639</v>
+        <v>3.294</v>
       </c>
       <c r="F41">
-        <v>5.0739</v>
+        <v>5.204000000000001</v>
       </c>
       <c r="G41">
         <v>1.35</v>
@@ -4649,28 +4649,28 @@
         <v>2.151</v>
       </c>
       <c r="M41">
-        <v>0.27145365</v>
+        <v>0.2784140000000001</v>
       </c>
       <c r="N41">
-        <v>1.87954635</v>
+        <v>1.872586</v>
       </c>
       <c r="O41">
-        <v>0.3571138065</v>
+        <v>0.35579134</v>
       </c>
       <c r="P41">
-        <v>1.5224325435</v>
+        <v>1.51679466</v>
       </c>
       <c r="Q41">
-        <v>2.2014325435</v>
+        <v>2.19579466</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1137308673153274</v>
+        <v>0.1147213270936586</v>
       </c>
       <c r="T41">
-        <v>1.324099043632573</v>
+        <v>1.343404948254066</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.924004705775737</v>
+        <v>7.725904588131342</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08616679625619517</v>
+        <v>0.08632279345004067</v>
       </c>
       <c r="C42">
-        <v>8.071666620554383</v>
+        <v>7.930964207386409</v>
       </c>
       <c r="D42">
-        <v>11.92566662055438</v>
+        <v>11.91506420738641</v>
       </c>
       <c r="E42">
-        <v>3.294</v>
+        <v>3.4241</v>
       </c>
       <c r="F42">
-        <v>5.204000000000001</v>
+        <v>5.3341</v>
       </c>
       <c r="G42">
         <v>1.35</v>
@@ -4731,45 +4731,45 @@
         <v>2.151</v>
       </c>
       <c r="M42">
-        <v>0.2784140000000001</v>
+        <v>0.28964163</v>
       </c>
       <c r="N42">
-        <v>1.872586</v>
+        <v>1.86135837</v>
       </c>
       <c r="O42">
-        <v>0.35579134</v>
+        <v>0.3536580902999999</v>
       </c>
       <c r="P42">
-        <v>1.51679466</v>
+        <v>1.5077002797</v>
       </c>
       <c r="Q42">
-        <v>2.19579466</v>
+        <v>2.1867002797</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1147213270936586</v>
+        <v>0.1157453617797299</v>
       </c>
       <c r="T42">
-        <v>1.343404948254066</v>
+        <v>1.363365290320354</v>
       </c>
       <c r="U42">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V42">
         <v>0.19</v>
       </c>
       <c r="W42">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y42">
-        <v>7.725904588131342</v>
+        <v>7.426418640165778</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08632279345004067</v>
+        <v>0.08621959064388615</v>
       </c>
       <c r="C43">
-        <v>7.930964207386409</v>
+        <v>7.807876316693741</v>
       </c>
       <c r="D43">
-        <v>11.91506420738641</v>
+        <v>11.92207631669374</v>
       </c>
       <c r="E43">
-        <v>3.4241</v>
+        <v>3.554200000000001</v>
       </c>
       <c r="F43">
-        <v>5.3341</v>
+        <v>5.464200000000001</v>
       </c>
       <c r="G43">
         <v>1.35</v>
@@ -4813,28 +4813,28 @@
         <v>2.151</v>
       </c>
       <c r="M43">
-        <v>0.28964163</v>
+        <v>0.29670606</v>
       </c>
       <c r="N43">
-        <v>1.86135837</v>
+        <v>1.85429394</v>
       </c>
       <c r="O43">
-        <v>0.3536580902999999</v>
+        <v>0.3523158486</v>
       </c>
       <c r="P43">
-        <v>1.5077002797</v>
+        <v>1.5019780914</v>
       </c>
       <c r="Q43">
-        <v>2.1867002797</v>
+        <v>2.1809780914</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1157453617797299</v>
+        <v>0.1168047080067003</v>
       </c>
       <c r="T43">
-        <v>1.363365290320354</v>
+        <v>1.384013920044101</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.426418640165778</v>
+        <v>7.249599148733259</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08621959064388615</v>
+        <v>0.08611638783773164</v>
       </c>
       <c r="C44">
-        <v>7.807876316693742</v>
+        <v>7.684796684224426</v>
       </c>
       <c r="D44">
-        <v>11.92207631669374</v>
+        <v>11.92909668422443</v>
       </c>
       <c r="E44">
-        <v>3.5542</v>
+        <v>3.684299999999999</v>
       </c>
       <c r="F44">
-        <v>5.4642</v>
+        <v>5.5943</v>
       </c>
       <c r="G44">
         <v>1.35</v>
@@ -4895,28 +4895,28 @@
         <v>2.151</v>
       </c>
       <c r="M44">
-        <v>0.29670606</v>
+        <v>0.30377049</v>
       </c>
       <c r="N44">
-        <v>1.85429394</v>
+        <v>1.84722951</v>
       </c>
       <c r="O44">
-        <v>0.3523158486</v>
+        <v>0.3509736069</v>
       </c>
       <c r="P44">
-        <v>1.5019780914</v>
+        <v>1.4962559031</v>
       </c>
       <c r="Q44">
-        <v>2.1809780914</v>
+        <v>2.1752559031</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1168047080067003</v>
+        <v>0.1179012242767222</v>
       </c>
       <c r="T44">
-        <v>1.384013920044101</v>
+        <v>1.405387063091488</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.249599148733261</v>
+        <v>7.081003819692953</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08611638783773164</v>
+        <v>0.08601318503157712</v>
       </c>
       <c r="C45">
-        <v>7.684796684224426</v>
+        <v>7.561725324575725</v>
       </c>
       <c r="D45">
-        <v>11.92909668422443</v>
+        <v>11.93612532457573</v>
       </c>
       <c r="E45">
-        <v>3.684299999999999</v>
+        <v>3.8144</v>
       </c>
       <c r="F45">
-        <v>5.5943</v>
+        <v>5.7244</v>
       </c>
       <c r="G45">
         <v>1.35</v>
@@ -4977,28 +4977,28 @@
         <v>2.151</v>
       </c>
       <c r="M45">
-        <v>0.30377049</v>
+        <v>0.31083492</v>
       </c>
       <c r="N45">
-        <v>1.84722951</v>
+        <v>1.84016508</v>
       </c>
       <c r="O45">
-        <v>0.3509736069</v>
+        <v>0.3496313652</v>
       </c>
       <c r="P45">
-        <v>1.4962559031</v>
+        <v>1.4905337148</v>
       </c>
       <c r="Q45">
-        <v>2.1752559031</v>
+        <v>2.1695337148</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1179012242767222</v>
+        <v>0.119036901842102</v>
       </c>
       <c r="T45">
-        <v>1.405387063091488</v>
+        <v>1.427523532676282</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.081003819692953</v>
+        <v>6.92007191469993</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08601318503157712</v>
+        <v>0.08590998222542259</v>
       </c>
       <c r="C46">
-        <v>7.561725324575725</v>
+        <v>7.438662252379341</v>
       </c>
       <c r="D46">
-        <v>11.93612532457573</v>
+        <v>11.94316225237934</v>
       </c>
       <c r="E46">
-        <v>3.8144</v>
+        <v>3.9445</v>
       </c>
       <c r="F46">
-        <v>5.7244</v>
+        <v>5.8545</v>
       </c>
       <c r="G46">
         <v>1.35</v>
@@ -5059,28 +5059,28 @@
         <v>2.151</v>
       </c>
       <c r="M46">
-        <v>0.31083492</v>
+        <v>0.31789935</v>
       </c>
       <c r="N46">
-        <v>1.84016508</v>
+        <v>1.83310065</v>
       </c>
       <c r="O46">
-        <v>0.3496313652</v>
+        <v>0.3482891235</v>
       </c>
       <c r="P46">
-        <v>1.4905337148</v>
+        <v>1.4848115265</v>
       </c>
       <c r="Q46">
-        <v>2.1695337148</v>
+        <v>2.1638115265</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.119036901842102</v>
+        <v>0.1202138767734956</v>
       </c>
       <c r="T46">
-        <v>1.427523532676282</v>
+        <v>1.450464964791432</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.92007191469993</v>
+        <v>6.76629253881771</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08590998222542259</v>
+        <v>0.08580677941926809</v>
       </c>
       <c r="C47">
-        <v>7.438662252379341</v>
+        <v>7.315607482301481</v>
       </c>
       <c r="D47">
-        <v>11.94316225237934</v>
+        <v>11.95020748230148</v>
       </c>
       <c r="E47">
-        <v>3.9445</v>
+        <v>4.0746</v>
       </c>
       <c r="F47">
-        <v>5.8545</v>
+        <v>5.9846</v>
       </c>
       <c r="G47">
         <v>1.35</v>
@@ -5141,28 +5141,28 @@
         <v>2.151</v>
       </c>
       <c r="M47">
-        <v>0.31789935</v>
+        <v>0.32496378</v>
       </c>
       <c r="N47">
-        <v>1.83310065</v>
+        <v>1.82603622</v>
       </c>
       <c r="O47">
-        <v>0.3482891235</v>
+        <v>0.3469468817999999</v>
       </c>
       <c r="P47">
-        <v>1.4848115265</v>
+        <v>1.4790893382</v>
       </c>
       <c r="Q47">
-        <v>2.1638115265</v>
+        <v>2.1580893382</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1202138767734956</v>
+        <v>0.121434443369015</v>
       </c>
       <c r="T47">
-        <v>1.450464964791432</v>
+        <v>1.474256079577513</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.76629253881771</v>
+        <v>6.619199222756455</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08580677941926809</v>
+        <v>0.08570357661311358</v>
       </c>
       <c r="C48">
-        <v>7.315607482301481</v>
+        <v>7.192561029043</v>
       </c>
       <c r="D48">
-        <v>11.95020748230148</v>
+        <v>11.957261029043</v>
       </c>
       <c r="E48">
-        <v>4.0746</v>
+        <v>4.2047</v>
       </c>
       <c r="F48">
-        <v>5.9846</v>
+        <v>6.1147</v>
       </c>
       <c r="G48">
         <v>1.35</v>
@@ -5223,28 +5223,28 @@
         <v>2.151</v>
       </c>
       <c r="M48">
-        <v>0.32496378</v>
+        <v>0.33202821</v>
       </c>
       <c r="N48">
-        <v>1.82603622</v>
+        <v>1.81897179</v>
       </c>
       <c r="O48">
-        <v>0.3469468817999999</v>
+        <v>0.3456046401</v>
       </c>
       <c r="P48">
-        <v>1.4790893382</v>
+        <v>1.4733671499</v>
       </c>
       <c r="Q48">
-        <v>2.1580893382</v>
+        <v>2.1523671499</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.121434443369015</v>
+        <v>0.1227010690813464</v>
       </c>
       <c r="T48">
-        <v>1.474256079577513</v>
+        <v>1.498944972280051</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.619199222756455</v>
+        <v>6.478365196740361</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08570357661311358</v>
+        <v>0.08560037380695908</v>
       </c>
       <c r="C49">
-        <v>7.192561029043</v>
+        <v>7.069522907339464</v>
       </c>
       <c r="D49">
-        <v>11.957261029043</v>
+        <v>11.96432290733947</v>
       </c>
       <c r="E49">
-        <v>4.2047</v>
+        <v>4.3348</v>
       </c>
       <c r="F49">
-        <v>6.1147</v>
+        <v>6.244800000000001</v>
       </c>
       <c r="G49">
         <v>1.35</v>
@@ -5305,28 +5305,28 @@
         <v>2.151</v>
       </c>
       <c r="M49">
-        <v>0.33202821</v>
+        <v>0.3390926400000001</v>
       </c>
       <c r="N49">
-        <v>1.81897179</v>
+        <v>1.81190736</v>
       </c>
       <c r="O49">
-        <v>0.3456046401</v>
+        <v>0.3442623983999999</v>
       </c>
       <c r="P49">
-        <v>1.4733671499</v>
+        <v>1.4676449616</v>
       </c>
       <c r="Q49">
-        <v>2.1523671499</v>
+        <v>2.1466449616</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1227010690813464</v>
+        <v>0.124016411167229</v>
       </c>
       <c r="T49">
-        <v>1.498944972280051</v>
+        <v>1.52458343777884</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.478365196740361</v>
+        <v>6.343399255141602</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08560037380695906</v>
+        <v>0.08549717100080456</v>
       </c>
       <c r="C50">
-        <v>7.069522907339469</v>
+        <v>6.946493131961286</v>
       </c>
       <c r="D50">
-        <v>11.96432290733947</v>
+        <v>11.97139313196129</v>
       </c>
       <c r="E50">
-        <v>4.3348</v>
+        <v>4.464899999999999</v>
       </c>
       <c r="F50">
-        <v>6.2448</v>
+        <v>6.374899999999999</v>
       </c>
       <c r="G50">
         <v>1.35</v>
@@ -5387,28 +5387,28 @@
         <v>2.151</v>
       </c>
       <c r="M50">
-        <v>0.33909264</v>
+        <v>0.34615707</v>
       </c>
       <c r="N50">
-        <v>1.81190736</v>
+        <v>1.80484293</v>
       </c>
       <c r="O50">
-        <v>0.3442623983999999</v>
+        <v>0.3429201567</v>
       </c>
       <c r="P50">
-        <v>1.4676449616</v>
+        <v>1.4619227733</v>
       </c>
       <c r="Q50">
-        <v>2.1466449616</v>
+        <v>2.1409227733</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.124016411167229</v>
+        <v>0.1253833352956952</v>
       </c>
       <c r="T50">
-        <v>1.524583437778839</v>
+        <v>1.551227333297189</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.343399255141603</v>
+        <v>6.213942127485653</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08549717100080456</v>
+        <v>0.08579896819465004</v>
       </c>
       <c r="C51">
-        <v>6.946493131961286</v>
+        <v>6.795741060768978</v>
       </c>
       <c r="D51">
-        <v>11.97139313196129</v>
+        <v>11.95074106076898</v>
       </c>
       <c r="E51">
-        <v>4.464899999999999</v>
+        <v>4.595</v>
       </c>
       <c r="F51">
-        <v>6.374899999999999</v>
+        <v>6.505</v>
       </c>
       <c r="G51">
         <v>1.35</v>
@@ -5469,45 +5469,45 @@
         <v>2.151</v>
       </c>
       <c r="M51">
-        <v>0.34615707</v>
+        <v>0.3597265</v>
       </c>
       <c r="N51">
-        <v>1.80484293</v>
+        <v>1.7912735</v>
       </c>
       <c r="O51">
-        <v>0.3429201567</v>
+        <v>0.340341965</v>
       </c>
       <c r="P51">
-        <v>1.4619227733</v>
+        <v>1.450931535</v>
       </c>
       <c r="Q51">
-        <v>2.1409227733</v>
+        <v>2.129931535</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1253833352956952</v>
+        <v>0.1268049363893001</v>
       </c>
       <c r="T51">
-        <v>1.551227333297189</v>
+        <v>1.578936984636272</v>
       </c>
       <c r="U51">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V51">
         <v>0.19</v>
       </c>
       <c r="W51">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>6.213942127485653</v>
+        <v>5.979542791537459</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08579896819465004</v>
+        <v>0.08570386538849553</v>
       </c>
       <c r="C52">
-        <v>6.795741060768978</v>
+        <v>6.672141280650217</v>
       </c>
       <c r="D52">
-        <v>11.95074106076898</v>
+        <v>11.95724128065022</v>
       </c>
       <c r="E52">
-        <v>4.595</v>
+        <v>4.7251</v>
       </c>
       <c r="F52">
-        <v>6.505</v>
+        <v>6.6351</v>
       </c>
       <c r="G52">
         <v>1.35</v>
@@ -5551,28 +5551,28 @@
         <v>2.151</v>
       </c>
       <c r="M52">
-        <v>0.3597265</v>
+        <v>0.36692103</v>
       </c>
       <c r="N52">
-        <v>1.7912735</v>
+        <v>1.78407897</v>
       </c>
       <c r="O52">
-        <v>0.340341965</v>
+        <v>0.3389750042999999</v>
       </c>
       <c r="P52">
-        <v>1.450931535</v>
+        <v>1.4451039657</v>
       </c>
       <c r="Q52">
-        <v>2.129931535</v>
+        <v>2.1241039657</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1268049363893001</v>
+        <v>0.1282845620173378</v>
       </c>
       <c r="T52">
-        <v>1.578936984636272</v>
+        <v>1.607777642152461</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.979542791537459</v>
+        <v>5.862296854448489</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08570386538849553</v>
+        <v>0.08560876258234101</v>
       </c>
       <c r="C53">
-        <v>6.672141280650217</v>
+        <v>6.548548575549297</v>
       </c>
       <c r="D53">
-        <v>11.95724128065022</v>
+        <v>11.9637485755493</v>
       </c>
       <c r="E53">
-        <v>4.7251</v>
+        <v>4.8552</v>
       </c>
       <c r="F53">
-        <v>6.6351</v>
+        <v>6.7652</v>
       </c>
       <c r="G53">
         <v>1.35</v>
@@ -5633,28 +5633,28 @@
         <v>2.151</v>
       </c>
       <c r="M53">
-        <v>0.36692103</v>
+        <v>0.37411556</v>
       </c>
       <c r="N53">
-        <v>1.78407897</v>
+        <v>1.77688444</v>
       </c>
       <c r="O53">
-        <v>0.3389750042999999</v>
+        <v>0.3376080436</v>
       </c>
       <c r="P53">
-        <v>1.4451039657</v>
+        <v>1.4392763964</v>
       </c>
       <c r="Q53">
-        <v>2.1241039657</v>
+        <v>2.1182763964</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1282845620173378</v>
+        <v>0.1298258387132104</v>
       </c>
       <c r="T53">
-        <v>1.607777642152461</v>
+        <v>1.637819993731823</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.862296854448489</v>
+        <v>5.749560376478327</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08560876258234101</v>
+        <v>0.0855136597761865</v>
       </c>
       <c r="C54">
-        <v>6.548548575549297</v>
+        <v>6.424962957023467</v>
       </c>
       <c r="D54">
-        <v>11.9637485755493</v>
+        <v>11.97026295702347</v>
       </c>
       <c r="E54">
-        <v>4.8552</v>
+        <v>4.985300000000001</v>
       </c>
       <c r="F54">
-        <v>6.7652</v>
+        <v>6.895300000000001</v>
       </c>
       <c r="G54">
         <v>1.35</v>
@@ -5715,28 +5715,28 @@
         <v>2.151</v>
       </c>
       <c r="M54">
-        <v>0.37411556</v>
+        <v>0.38131009</v>
       </c>
       <c r="N54">
-        <v>1.77688444</v>
+        <v>1.76968991</v>
       </c>
       <c r="O54">
-        <v>0.3376080436</v>
+        <v>0.3362410829</v>
       </c>
       <c r="P54">
-        <v>1.4392763964</v>
+        <v>1.4334488271</v>
       </c>
       <c r="Q54">
-        <v>2.1182763964</v>
+        <v>2.1124488271</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1298258387132104</v>
+        <v>0.1314327016514606</v>
       </c>
       <c r="T54">
-        <v>1.637819993731823</v>
+        <v>1.669140743250734</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.749560376478327</v>
+        <v>5.641078105224017</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0855136597761865</v>
+        <v>0.08541855697003198</v>
       </c>
       <c r="C55">
-        <v>6.424962957023467</v>
+        <v>6.301384436655172</v>
       </c>
       <c r="D55">
-        <v>11.97026295702347</v>
+        <v>11.97678443665517</v>
       </c>
       <c r="E55">
-        <v>4.985300000000001</v>
+        <v>5.1154</v>
       </c>
       <c r="F55">
-        <v>6.895300000000001</v>
+        <v>7.0254</v>
       </c>
       <c r="G55">
         <v>1.35</v>
@@ -5797,28 +5797,28 @@
         <v>2.151</v>
       </c>
       <c r="M55">
-        <v>0.38131009</v>
+        <v>0.38850462</v>
       </c>
       <c r="N55">
-        <v>1.76968991</v>
+        <v>1.76249538</v>
       </c>
       <c r="O55">
-        <v>0.3362410829</v>
+        <v>0.3348741222</v>
       </c>
       <c r="P55">
-        <v>1.4334488271</v>
+        <v>1.4276212578</v>
       </c>
       <c r="Q55">
-        <v>2.1124488271</v>
+        <v>2.1066212578</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1314327016514606</v>
+        <v>0.1331094281957217</v>
       </c>
       <c r="T55">
-        <v>1.669140743250734</v>
+        <v>1.701823264487858</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.641078105224017</v>
+        <v>5.536613695868017</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08541855697003198</v>
+        <v>0.08532345416387746</v>
       </c>
       <c r="C56">
-        <v>6.301384436655172</v>
+        <v>6.177813026052109</v>
       </c>
       <c r="D56">
-        <v>11.97678443665517</v>
+        <v>11.98331302605211</v>
       </c>
       <c r="E56">
-        <v>5.1154</v>
+        <v>5.245500000000001</v>
       </c>
       <c r="F56">
-        <v>7.0254</v>
+        <v>7.155500000000001</v>
       </c>
       <c r="G56">
         <v>1.35</v>
@@ -5879,28 +5879,28 @@
         <v>2.151</v>
       </c>
       <c r="M56">
-        <v>0.38850462</v>
+        <v>0.3956991500000001</v>
       </c>
       <c r="N56">
-        <v>1.76249538</v>
+        <v>1.75530085</v>
       </c>
       <c r="O56">
-        <v>0.3348741222</v>
+        <v>0.3335071615</v>
       </c>
       <c r="P56">
-        <v>1.4276212578</v>
+        <v>1.4217936885</v>
       </c>
       <c r="Q56">
-        <v>2.1066212578</v>
+        <v>2.1007936885</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1331094281957217</v>
+        <v>0.1348606759197277</v>
       </c>
       <c r="T56">
-        <v>1.701823264487858</v>
+        <v>1.735958342224409</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.536613695868017</v>
+        <v>5.43594799230678</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08532345416387746</v>
+        <v>0.08522835135772296</v>
       </c>
       <c r="C57">
-        <v>6.177813026052109</v>
+        <v>6.054248736847292</v>
       </c>
       <c r="D57">
-        <v>11.98331302605211</v>
+        <v>11.98984873684729</v>
       </c>
       <c r="E57">
-        <v>5.245500000000001</v>
+        <v>5.3756</v>
       </c>
       <c r="F57">
-        <v>7.155500000000001</v>
+        <v>7.285600000000001</v>
       </c>
       <c r="G57">
         <v>1.35</v>
@@ -5961,28 +5961,28 @@
         <v>2.151</v>
       </c>
       <c r="M57">
-        <v>0.3956991500000001</v>
+        <v>0.40289368</v>
       </c>
       <c r="N57">
-        <v>1.75530085</v>
+        <v>1.74810632</v>
       </c>
       <c r="O57">
-        <v>0.3335071615</v>
+        <v>0.3321402008</v>
       </c>
       <c r="P57">
-        <v>1.4217936885</v>
+        <v>1.4159661192</v>
       </c>
       <c r="Q57">
-        <v>2.1007936885</v>
+        <v>2.0949661192</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1348606759197277</v>
+        <v>0.1366915258130067</v>
       </c>
       <c r="T57">
-        <v>1.735958342224409</v>
+        <v>1.771645014403532</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.43594799230678</v>
+        <v>5.338877492444159</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08522835135772296</v>
+        <v>0.08513324855156844</v>
       </c>
       <c r="C58">
-        <v>6.054248736847292</v>
+        <v>5.930691580699136</v>
       </c>
       <c r="D58">
-        <v>11.98984873684729</v>
+        <v>11.99639158069914</v>
       </c>
       <c r="E58">
-        <v>5.3756</v>
+        <v>5.505700000000001</v>
       </c>
       <c r="F58">
-        <v>7.285600000000001</v>
+        <v>7.415700000000001</v>
       </c>
       <c r="G58">
         <v>1.35</v>
@@ -6043,28 +6043,28 @@
         <v>2.151</v>
       </c>
       <c r="M58">
-        <v>0.40289368</v>
+        <v>0.4100882100000001</v>
       </c>
       <c r="N58">
-        <v>1.74810632</v>
+        <v>1.74091179</v>
       </c>
       <c r="O58">
-        <v>0.3321402008</v>
+        <v>0.3307732401</v>
       </c>
       <c r="P58">
-        <v>1.4159661192</v>
+        <v>1.4101385499</v>
       </c>
       <c r="Q58">
-        <v>2.0949661192</v>
+        <v>2.089138549899999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1366915258130067</v>
+        <v>0.1386075315152754</v>
       </c>
       <c r="T58">
-        <v>1.771645014403532</v>
+        <v>1.808991531800287</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.338877492444159</v>
+        <v>5.245212975032858</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08513324855156844</v>
+        <v>0.08503814574541393</v>
       </c>
       <c r="C59">
-        <v>5.930691580699136</v>
+        <v>5.807141569291514</v>
       </c>
       <c r="D59">
-        <v>11.99639158069914</v>
+        <v>12.00294156929152</v>
       </c>
       <c r="E59">
-        <v>5.505700000000001</v>
+        <v>5.635800000000001</v>
       </c>
       <c r="F59">
-        <v>7.415700000000001</v>
+        <v>7.545800000000001</v>
       </c>
       <c r="G59">
         <v>1.35</v>
@@ -6125,28 +6125,28 @@
         <v>2.151</v>
       </c>
       <c r="M59">
-        <v>0.4100882100000001</v>
+        <v>0.41728274</v>
       </c>
       <c r="N59">
-        <v>1.74091179</v>
+        <v>1.73371726</v>
       </c>
       <c r="O59">
-        <v>0.3307732401</v>
+        <v>0.3294062793999999</v>
       </c>
       <c r="P59">
-        <v>1.4101385499</v>
+        <v>1.4043109806</v>
       </c>
       <c r="Q59">
-        <v>2.089138549899999</v>
+        <v>2.0833109806</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1386075315152754</v>
+        <v>0.1406147755843189</v>
       </c>
       <c r="T59">
-        <v>1.808991531800287</v>
+        <v>1.848116454787365</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.245212975032858</v>
+        <v>5.154778268566774</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08503814574541392</v>
+        <v>0.08494304293925942</v>
       </c>
       <c r="C60">
-        <v>5.807141569291516</v>
+        <v>5.68359871433383</v>
       </c>
       <c r="D60">
-        <v>12.00294156929152</v>
+        <v>12.00949871433383</v>
       </c>
       <c r="E60">
-        <v>5.635799999999999</v>
+        <v>5.765899999999999</v>
       </c>
       <c r="F60">
-        <v>7.545799999999999</v>
+        <v>7.6759</v>
       </c>
       <c r="G60">
         <v>1.35</v>
@@ -6207,28 +6207,28 @@
         <v>2.151</v>
       </c>
       <c r="M60">
-        <v>0.4172827399999999</v>
+        <v>0.42447727</v>
       </c>
       <c r="N60">
-        <v>1.73371726</v>
+        <v>1.72652273</v>
       </c>
       <c r="O60">
-        <v>0.3294062794</v>
+        <v>0.3280393187</v>
       </c>
       <c r="P60">
-        <v>1.4043109806</v>
+        <v>1.3984834113</v>
       </c>
       <c r="Q60">
-        <v>2.0833109806</v>
+        <v>2.0774834113</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1406147755843188</v>
+        <v>0.1427199339981937</v>
       </c>
       <c r="T60">
-        <v>1.848116454787364</v>
+        <v>1.88914991060308</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.154778268566776</v>
+        <v>5.067409145370728</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08494304293925942</v>
+        <v>0.0848479401331049</v>
       </c>
       <c r="C61">
-        <v>5.68359871433383</v>
+        <v>5.560063027561091</v>
       </c>
       <c r="D61">
-        <v>12.00949871433383</v>
+        <v>12.01606302756109</v>
       </c>
       <c r="E61">
-        <v>5.765899999999999</v>
+        <v>5.895999999999999</v>
       </c>
       <c r="F61">
-        <v>7.6759</v>
+        <v>7.805999999999999</v>
       </c>
       <c r="G61">
         <v>1.35</v>
@@ -6289,28 +6289,28 @@
         <v>2.151</v>
       </c>
       <c r="M61">
-        <v>0.42447727</v>
+        <v>0.4316718</v>
       </c>
       <c r="N61">
-        <v>1.72652273</v>
+        <v>1.7193282</v>
       </c>
       <c r="O61">
-        <v>0.3280393187</v>
+        <v>0.326672358</v>
       </c>
       <c r="P61">
-        <v>1.3984834113</v>
+        <v>1.392655842</v>
       </c>
       <c r="Q61">
-        <v>2.0774834113</v>
+        <v>2.071655842</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1427199339981937</v>
+        <v>0.1449303503327622</v>
       </c>
       <c r="T61">
-        <v>1.88914991060308</v>
+        <v>1.932235039209581</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.067409145370728</v>
+        <v>4.982952326281216</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0848479401331049</v>
+        <v>0.08475283732695038</v>
       </c>
       <c r="C62">
-        <v>5.560063027561091</v>
+        <v>5.436534520733971</v>
       </c>
       <c r="D62">
-        <v>12.01606302756109</v>
+        <v>12.02263452073397</v>
       </c>
       <c r="E62">
-        <v>5.895999999999999</v>
+        <v>6.0261</v>
       </c>
       <c r="F62">
-        <v>7.805999999999999</v>
+        <v>7.9361</v>
       </c>
       <c r="G62">
         <v>1.35</v>
@@ -6371,28 +6371,28 @@
         <v>2.151</v>
       </c>
       <c r="M62">
-        <v>0.4316718</v>
+        <v>0.43886633</v>
       </c>
       <c r="N62">
-        <v>1.7193282</v>
+        <v>1.71213367</v>
       </c>
       <c r="O62">
-        <v>0.326672358</v>
+        <v>0.3253053973</v>
       </c>
       <c r="P62">
-        <v>1.392655842</v>
+        <v>1.3868282727</v>
       </c>
       <c r="Q62">
-        <v>2.071655842</v>
+        <v>2.0658282727</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1449303503327622</v>
+        <v>0.1472541213511548</v>
       </c>
       <c r="T62">
-        <v>1.932235039209581</v>
+        <v>1.977529661590775</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.982952326281216</v>
+        <v>4.901264583227425</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08475283732695038</v>
+        <v>0.08465773452079586</v>
       </c>
       <c r="C63">
-        <v>5.436534520733971</v>
+        <v>5.313013205638891</v>
       </c>
       <c r="D63">
-        <v>12.02263452073397</v>
+        <v>12.02921320563889</v>
       </c>
       <c r="E63">
-        <v>6.0261</v>
+        <v>6.1562</v>
       </c>
       <c r="F63">
-        <v>7.9361</v>
+        <v>8.0662</v>
       </c>
       <c r="G63">
         <v>1.35</v>
@@ -6453,28 +6453,28 @@
         <v>2.151</v>
       </c>
       <c r="M63">
-        <v>0.43886633</v>
+        <v>0.44606086</v>
       </c>
       <c r="N63">
-        <v>1.71213367</v>
+        <v>1.70493914</v>
       </c>
       <c r="O63">
-        <v>0.3253053973</v>
+        <v>0.3239384366</v>
       </c>
       <c r="P63">
-        <v>1.3868282727</v>
+        <v>1.3810007034</v>
       </c>
       <c r="Q63">
-        <v>2.0658282727</v>
+        <v>2.0600007034</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1472541213511548</v>
+        <v>0.1497001961073575</v>
       </c>
       <c r="T63">
-        <v>1.977529661590775</v>
+        <v>2.025208211465715</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.901264583227425</v>
+        <v>4.822211928659241</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08465773452079586</v>
+        <v>0.08456263171464136</v>
       </c>
       <c r="C64">
-        <v>5.313013205638891</v>
+        <v>5.189499094088077</v>
       </c>
       <c r="D64">
-        <v>12.02921320563889</v>
+        <v>12.03579909408808</v>
       </c>
       <c r="E64">
-        <v>6.1562</v>
+        <v>6.286300000000001</v>
       </c>
       <c r="F64">
-        <v>8.0662</v>
+        <v>8.196300000000001</v>
       </c>
       <c r="G64">
         <v>1.35</v>
@@ -6535,28 +6535,28 @@
         <v>2.151</v>
       </c>
       <c r="M64">
-        <v>0.44606086</v>
+        <v>0.45325539</v>
       </c>
       <c r="N64">
-        <v>1.70493914</v>
+        <v>1.69774461</v>
       </c>
       <c r="O64">
-        <v>0.3239384366</v>
+        <v>0.3225714759</v>
       </c>
       <c r="P64">
-        <v>1.3810007034</v>
+        <v>1.3751731341</v>
       </c>
       <c r="Q64">
-        <v>2.0600007034</v>
+        <v>2.0541731341</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1497001961073575</v>
+        <v>0.1522784911206523</v>
       </c>
       <c r="T64">
-        <v>2.025208211465715</v>
+        <v>2.075463980252815</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.822211928659241</v>
+        <v>4.745668882172586</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08456263171464136</v>
+        <v>0.08446752890848684</v>
       </c>
       <c r="C65">
-        <v>5.189499094088077</v>
+        <v>5.065992197919652</v>
       </c>
       <c r="D65">
-        <v>12.03579909408808</v>
+        <v>12.04239219791965</v>
       </c>
       <c r="E65">
-        <v>6.286300000000001</v>
+        <v>6.416399999999999</v>
       </c>
       <c r="F65">
-        <v>8.196300000000001</v>
+        <v>8.3264</v>
       </c>
       <c r="G65">
         <v>1.35</v>
@@ -6617,28 +6617,28 @@
         <v>2.151</v>
       </c>
       <c r="M65">
-        <v>0.45325539</v>
+        <v>0.46044992</v>
       </c>
       <c r="N65">
-        <v>1.69774461</v>
+        <v>1.69055008</v>
       </c>
       <c r="O65">
-        <v>0.3225714759</v>
+        <v>0.3212045151999999</v>
       </c>
       <c r="P65">
-        <v>1.3751731341</v>
+        <v>1.3693455648</v>
       </c>
       <c r="Q65">
-        <v>2.0541731341</v>
+        <v>2.0483455648</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1522784911206523</v>
+        <v>0.1550000247457968</v>
       </c>
       <c r="T65">
-        <v>2.075463980252815</v>
+        <v>2.128511736194753</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.745668882172586</v>
+        <v>4.671517805888639</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08446752890848684</v>
+        <v>0.08437242610233232</v>
       </c>
       <c r="C66">
-        <v>5.065992197919652</v>
+        <v>4.94249252899767</v>
       </c>
       <c r="D66">
-        <v>12.04239219791965</v>
+        <v>12.04899252899767</v>
       </c>
       <c r="E66">
-        <v>6.416399999999999</v>
+        <v>6.5465</v>
       </c>
       <c r="F66">
-        <v>8.3264</v>
+        <v>8.4565</v>
       </c>
       <c r="G66">
         <v>1.35</v>
@@ -6699,28 +6699,28 @@
         <v>2.151</v>
       </c>
       <c r="M66">
-        <v>0.46044992</v>
+        <v>0.46764445</v>
       </c>
       <c r="N66">
-        <v>1.69055008</v>
+        <v>1.68335555</v>
       </c>
       <c r="O66">
-        <v>0.3212045151999999</v>
+        <v>0.3198375545</v>
       </c>
       <c r="P66">
-        <v>1.3693455648</v>
+        <v>1.3635179955</v>
       </c>
       <c r="Q66">
-        <v>2.0483455648</v>
+        <v>2.0425179955</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1550000247457968</v>
+        <v>0.1578770745780924</v>
       </c>
       <c r="T66">
-        <v>2.128511736194753</v>
+        <v>2.184590792476231</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.671517805888639</v>
+        <v>4.59964830118266</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08437242610233232</v>
+        <v>0.08427732329617782</v>
       </c>
       <c r="C67">
-        <v>4.94249252899767</v>
+        <v>4.819000099212229</v>
       </c>
       <c r="D67">
-        <v>12.04899252899767</v>
+        <v>12.05560009921223</v>
       </c>
       <c r="E67">
-        <v>6.5465</v>
+        <v>6.676600000000001</v>
       </c>
       <c r="F67">
-        <v>8.4565</v>
+        <v>8.586600000000001</v>
       </c>
       <c r="G67">
         <v>1.35</v>
@@ -6781,28 +6781,28 @@
         <v>2.151</v>
       </c>
       <c r="M67">
-        <v>0.46764445</v>
+        <v>0.4748389800000001</v>
       </c>
       <c r="N67">
-        <v>1.68335555</v>
+        <v>1.67616102</v>
       </c>
       <c r="O67">
-        <v>0.3198375545</v>
+        <v>0.3184705937999999</v>
       </c>
       <c r="P67">
-        <v>1.3635179955</v>
+        <v>1.3576904262</v>
       </c>
       <c r="Q67">
-        <v>2.0425179955</v>
+        <v>2.0366904262</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1578770745780924</v>
+        <v>0.1609233626358171</v>
       </c>
       <c r="T67">
-        <v>2.184590792476231</v>
+        <v>2.243968616774266</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.59964830118266</v>
+        <v>4.52995666025565</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08427732329617782</v>
+        <v>0.08553897049002331</v>
       </c>
       <c r="C68">
-        <v>4.819000099212229</v>
+        <v>4.601828523215145</v>
       </c>
       <c r="D68">
-        <v>12.05560009921223</v>
+        <v>11.96852852321515</v>
       </c>
       <c r="E68">
-        <v>6.676600000000001</v>
+        <v>6.806700000000001</v>
       </c>
       <c r="F68">
-        <v>8.586600000000001</v>
+        <v>8.716700000000001</v>
       </c>
       <c r="G68">
         <v>1.35</v>
@@ -6863,45 +6863,45 @@
         <v>2.151</v>
       </c>
       <c r="M68">
-        <v>0.4748389800000001</v>
+        <v>0.5038252600000001</v>
       </c>
       <c r="N68">
-        <v>1.67616102</v>
+        <v>1.64717474</v>
       </c>
       <c r="O68">
-        <v>0.3184705937999999</v>
+        <v>0.3129632005999999</v>
       </c>
       <c r="P68">
-        <v>1.3576904262</v>
+        <v>1.3342115394</v>
       </c>
       <c r="Q68">
-        <v>2.0366904262</v>
+        <v>2.013211539399999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1609233626358171</v>
+        <v>0.1641542742121918</v>
       </c>
       <c r="T68">
-        <v>2.243968616774266</v>
+        <v>2.306945097090364</v>
       </c>
       <c r="U68">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V68">
         <v>0.19</v>
       </c>
       <c r="W68">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y68">
-        <v>4.52995666025565</v>
+        <v>4.269337349223021</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08553897049002331</v>
+        <v>0.0854641176838688</v>
       </c>
       <c r="C69">
-        <v>4.601828523215145</v>
+        <v>4.476859317817567</v>
       </c>
       <c r="D69">
-        <v>11.96852852321515</v>
+        <v>11.97365931781757</v>
       </c>
       <c r="E69">
-        <v>6.806700000000001</v>
+        <v>6.9368</v>
       </c>
       <c r="F69">
-        <v>8.716700000000001</v>
+        <v>8.8468</v>
       </c>
       <c r="G69">
         <v>1.35</v>
@@ -6945,28 +6945,28 @@
         <v>2.151</v>
       </c>
       <c r="M69">
-        <v>0.5038252600000001</v>
+        <v>0.51134504</v>
       </c>
       <c r="N69">
-        <v>1.64717474</v>
+        <v>1.63965496</v>
       </c>
       <c r="O69">
-        <v>0.3129632005999999</v>
+        <v>0.3115344423999999</v>
       </c>
       <c r="P69">
-        <v>1.3342115394</v>
+        <v>1.3281205176</v>
       </c>
       <c r="Q69">
-        <v>2.013211539399999</v>
+        <v>2.0071205176</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1641542742121918</v>
+        <v>0.16758711776209</v>
       </c>
       <c r="T69">
-        <v>2.306945097090364</v>
+        <v>2.373857607426218</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.269337349223021</v>
+        <v>4.20655297644033</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0854641176838688</v>
+        <v>0.08538926487771428</v>
       </c>
       <c r="C70">
-        <v>4.476859317817567</v>
+        <v>4.351894513352539</v>
       </c>
       <c r="D70">
-        <v>11.97365931781757</v>
+        <v>11.97879451335254</v>
       </c>
       <c r="E70">
-        <v>6.9368</v>
+        <v>7.0669</v>
       </c>
       <c r="F70">
-        <v>8.8468</v>
+        <v>8.976900000000001</v>
       </c>
       <c r="G70">
         <v>1.35</v>
@@ -7027,28 +7027,28 @@
         <v>2.151</v>
       </c>
       <c r="M70">
-        <v>0.51134504</v>
+        <v>0.5188648200000001</v>
       </c>
       <c r="N70">
-        <v>1.63965496</v>
+        <v>1.63213518</v>
       </c>
       <c r="O70">
-        <v>0.3115344423999999</v>
+        <v>0.3101056842</v>
       </c>
       <c r="P70">
-        <v>1.3281205176</v>
+        <v>1.3220294958</v>
       </c>
       <c r="Q70">
-        <v>2.0071205176</v>
+        <v>2.0010294958</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.16758711776209</v>
+        <v>0.1712414350894009</v>
       </c>
       <c r="T70">
-        <v>2.373857607426218</v>
+        <v>2.445087053912773</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.20655297644033</v>
+        <v>4.14558844054989</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08538926487771428</v>
+        <v>0.08531441207155976</v>
       </c>
       <c r="C71">
-        <v>4.351894513352539</v>
+        <v>4.226934115484834</v>
       </c>
       <c r="D71">
-        <v>11.97879451335254</v>
+        <v>11.98393411548484</v>
       </c>
       <c r="E71">
-        <v>7.0669</v>
+        <v>7.197000000000001</v>
       </c>
       <c r="F71">
-        <v>8.976900000000001</v>
+        <v>9.107000000000001</v>
       </c>
       <c r="G71">
         <v>1.35</v>
@@ -7109,28 +7109,28 @@
         <v>2.151</v>
       </c>
       <c r="M71">
-        <v>0.5188648200000001</v>
+        <v>0.5263846000000001</v>
       </c>
       <c r="N71">
-        <v>1.63213518</v>
+        <v>1.6246154</v>
       </c>
       <c r="O71">
-        <v>0.3101056842</v>
+        <v>0.308676926</v>
       </c>
       <c r="P71">
-        <v>1.3220294958</v>
+        <v>1.315938474</v>
       </c>
       <c r="Q71">
-        <v>2.0010294958</v>
+        <v>1.994938474</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1712414350894009</v>
+        <v>0.1751393735718659</v>
       </c>
       <c r="T71">
-        <v>2.445087053912773</v>
+        <v>2.521065130165097</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.14558844054989</v>
+        <v>4.086365748542034</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08531441207155976</v>
+        <v>0.08523955926540525</v>
       </c>
       <c r="C72">
-        <v>4.226934115484834</v>
+        <v>4.101978129888954</v>
       </c>
       <c r="D72">
-        <v>11.98393411548484</v>
+        <v>11.98907812988896</v>
       </c>
       <c r="E72">
-        <v>7.197000000000001</v>
+        <v>7.327100000000002</v>
       </c>
       <c r="F72">
-        <v>9.107000000000001</v>
+        <v>9.237100000000002</v>
       </c>
       <c r="G72">
         <v>1.35</v>
@@ -7191,28 +7191,28 @@
         <v>2.151</v>
       </c>
       <c r="M72">
-        <v>0.5263846000000001</v>
+        <v>0.5339043800000002</v>
       </c>
       <c r="N72">
-        <v>1.6246154</v>
+        <v>1.61709562</v>
       </c>
       <c r="O72">
-        <v>0.308676926</v>
+        <v>0.3072481678</v>
       </c>
       <c r="P72">
-        <v>1.315938474</v>
+        <v>1.3098474522</v>
       </c>
       <c r="Q72">
-        <v>1.994938474</v>
+        <v>1.9888474522</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1751393735718659</v>
+        <v>0.1793061353979492</v>
       </c>
       <c r="T72">
-        <v>2.521065130165097</v>
+        <v>2.602283073745169</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.086365748542034</v>
+        <v>4.02881130137947</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08523955926540526</v>
+        <v>0.08720590645925073</v>
       </c>
       <c r="C73">
-        <v>4.101978129888954</v>
+        <v>3.838196734001173</v>
       </c>
       <c r="D73">
-        <v>11.98907812988895</v>
+        <v>11.85539673400117</v>
       </c>
       <c r="E73">
-        <v>7.3271</v>
+        <v>7.457199999999998</v>
       </c>
       <c r="F73">
-        <v>9.2371</v>
+        <v>9.367199999999999</v>
       </c>
       <c r="G73">
         <v>1.35</v>
@@ -7273,45 +7273,45 @@
         <v>2.151</v>
       </c>
       <c r="M73">
-        <v>0.5339043800000001</v>
+        <v>0.5742093599999999</v>
       </c>
       <c r="N73">
-        <v>1.61709562</v>
+        <v>1.57679064</v>
       </c>
       <c r="O73">
-        <v>0.3072481678</v>
+        <v>0.2995902216</v>
       </c>
       <c r="P73">
-        <v>1.3098474522</v>
+        <v>1.2772004184</v>
       </c>
       <c r="Q73">
-        <v>1.9888474522</v>
+        <v>1.9562004184</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1793061353979491</v>
+        <v>0.1837705230687526</v>
       </c>
       <c r="T73">
-        <v>2.602283073745168</v>
+        <v>2.68930229900953</v>
       </c>
       <c r="U73">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V73">
         <v>0.19</v>
       </c>
       <c r="W73">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>4.028811301379471</v>
+        <v>3.746020441046102</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08720590645925073</v>
+        <v>0.08715940365309621</v>
       </c>
       <c r="C74">
-        <v>3.838196734001173</v>
+        <v>3.711223783589087</v>
       </c>
       <c r="D74">
-        <v>11.85539673400117</v>
+        <v>11.85852378358909</v>
       </c>
       <c r="E74">
-        <v>7.457199999999998</v>
+        <v>7.587299999999999</v>
       </c>
       <c r="F74">
-        <v>9.367199999999999</v>
+        <v>9.497299999999999</v>
       </c>
       <c r="G74">
         <v>1.35</v>
@@ -7355,28 +7355,28 @@
         <v>2.151</v>
       </c>
       <c r="M74">
-        <v>0.5742093599999999</v>
+        <v>0.5821844899999999</v>
       </c>
       <c r="N74">
-        <v>1.57679064</v>
+        <v>1.56881551</v>
       </c>
       <c r="O74">
-        <v>0.2995902216</v>
+        <v>0.2980749469</v>
       </c>
       <c r="P74">
-        <v>1.2772004184</v>
+        <v>1.2707405631</v>
       </c>
       <c r="Q74">
-        <v>1.9562004184</v>
+        <v>1.9497405631</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1837705230687526</v>
+        <v>0.1885656061225786</v>
       </c>
       <c r="T74">
-        <v>2.68930229900953</v>
+        <v>2.782767392811992</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.746020441046102</v>
+        <v>3.694705092538621</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08715940365309621</v>
+        <v>0.0871129008469417</v>
       </c>
       <c r="C75">
-        <v>3.711223783589087</v>
+        <v>3.584252483230435</v>
       </c>
       <c r="D75">
-        <v>11.85852378358909</v>
+        <v>11.86165248323043</v>
       </c>
       <c r="E75">
-        <v>7.587299999999999</v>
+        <v>7.7174</v>
       </c>
       <c r="F75">
-        <v>9.497299999999999</v>
+        <v>9.6274</v>
       </c>
       <c r="G75">
         <v>1.35</v>
@@ -7437,28 +7437,28 @@
         <v>2.151</v>
       </c>
       <c r="M75">
-        <v>0.5821844899999999</v>
+        <v>0.59015962</v>
       </c>
       <c r="N75">
-        <v>1.56881551</v>
+        <v>1.56084038</v>
       </c>
       <c r="O75">
-        <v>0.2980749469</v>
+        <v>0.2965596722</v>
       </c>
       <c r="P75">
-        <v>1.2707405631</v>
+        <v>1.2642807078</v>
       </c>
       <c r="Q75">
-        <v>1.9497405631</v>
+        <v>1.9432807078</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1885656061225786</v>
+        <v>0.1937295417190065</v>
       </c>
       <c r="T75">
-        <v>2.782767392811992</v>
+        <v>2.883422109214645</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.694705092538621</v>
+        <v>3.644776645342153</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0871129008469417</v>
+        <v>0.0870663980407872</v>
       </c>
       <c r="C76">
-        <v>3.584252483230435</v>
+        <v>3.457282834231584</v>
       </c>
       <c r="D76">
-        <v>11.86165248323043</v>
+        <v>11.86478283423159</v>
       </c>
       <c r="E76">
-        <v>7.7174</v>
+        <v>7.8475</v>
       </c>
       <c r="F76">
-        <v>9.6274</v>
+        <v>9.7575</v>
       </c>
       <c r="G76">
         <v>1.35</v>
@@ -7519,28 +7519,28 @@
         <v>2.151</v>
       </c>
       <c r="M76">
-        <v>0.59015962</v>
+        <v>0.59813475</v>
       </c>
       <c r="N76">
-        <v>1.56084038</v>
+        <v>1.55286525</v>
       </c>
       <c r="O76">
-        <v>0.2965596722</v>
+        <v>0.2950443974999999</v>
       </c>
       <c r="P76">
-        <v>1.2642807078</v>
+        <v>1.2578208525</v>
       </c>
       <c r="Q76">
-        <v>1.9432807078</v>
+        <v>1.9368208525</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1937295417190065</v>
+        <v>0.1993065921631487</v>
       </c>
       <c r="T76">
-        <v>2.883422109214645</v>
+        <v>2.992129202929509</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.644776645342153</v>
+        <v>3.596179623404257</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0870663980407872</v>
+        <v>0.08701989523463269</v>
       </c>
       <c r="C77">
-        <v>3.457282834231584</v>
+        <v>3.330314837900291</v>
       </c>
       <c r="D77">
-        <v>11.86478283423159</v>
+        <v>11.86791483790029</v>
       </c>
       <c r="E77">
-        <v>7.8475</v>
+        <v>7.977600000000001</v>
       </c>
       <c r="F77">
-        <v>9.7575</v>
+        <v>9.887600000000001</v>
       </c>
       <c r="G77">
         <v>1.35</v>
@@ -7601,28 +7601,28 @@
         <v>2.151</v>
       </c>
       <c r="M77">
-        <v>0.59813475</v>
+        <v>0.6061098800000001</v>
       </c>
       <c r="N77">
-        <v>1.55286525</v>
+        <v>1.54489012</v>
       </c>
       <c r="O77">
-        <v>0.2950443974999999</v>
+        <v>0.2935291228</v>
       </c>
       <c r="P77">
-        <v>1.2578208525</v>
+        <v>1.2513609972</v>
       </c>
       <c r="Q77">
-        <v>1.9368208525</v>
+        <v>1.9303609972</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1993065921631487</v>
+        <v>0.2053483968109695</v>
       </c>
       <c r="T77">
-        <v>2.992129202929509</v>
+        <v>3.109895221120613</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.596179623404257</v>
+        <v>3.548861470464728</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08701989523463269</v>
+        <v>0.08697339242847818</v>
       </c>
       <c r="C78">
-        <v>3.330314837900291</v>
+        <v>3.203348495545685</v>
       </c>
       <c r="D78">
-        <v>11.86791483790029</v>
+        <v>11.87104849554568</v>
       </c>
       <c r="E78">
-        <v>7.977600000000001</v>
+        <v>8.107699999999999</v>
       </c>
       <c r="F78">
-        <v>9.887600000000001</v>
+        <v>10.0177</v>
       </c>
       <c r="G78">
         <v>1.35</v>
@@ -7683,28 +7683,28 @@
         <v>2.151</v>
       </c>
       <c r="M78">
-        <v>0.6061098800000001</v>
+        <v>0.6140850099999999</v>
       </c>
       <c r="N78">
-        <v>1.54489012</v>
+        <v>1.53691499</v>
       </c>
       <c r="O78">
-        <v>0.2935291228</v>
+        <v>0.2920138481</v>
       </c>
       <c r="P78">
-        <v>1.2513609972</v>
+        <v>1.2449011419</v>
       </c>
       <c r="Q78">
-        <v>1.9303609972</v>
+        <v>1.9239011419</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2053483968109695</v>
+        <v>0.211915575775992</v>
       </c>
       <c r="T78">
-        <v>3.109895221120613</v>
+        <v>3.237901762632682</v>
       </c>
       <c r="U78">
         <v>0.0613</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.548861470464728</v>
+        <v>3.502772360458693</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08697339242847818</v>
+        <v>0.08869592962232366</v>
       </c>
       <c r="C79">
-        <v>3.203348495545685</v>
+        <v>2.958266823444385</v>
       </c>
       <c r="D79">
-        <v>11.87104849554568</v>
+        <v>11.75606682344439</v>
       </c>
       <c r="E79">
-        <v>8.107699999999999</v>
+        <v>8.2378</v>
       </c>
       <c r="F79">
-        <v>10.0177</v>
+        <v>10.1478</v>
       </c>
       <c r="G79">
         <v>1.35</v>
@@ -7765,45 +7765,45 @@
         <v>2.151</v>
       </c>
       <c r="M79">
-        <v>0.6140850099999999</v>
+        <v>0.65047398</v>
       </c>
       <c r="N79">
-        <v>1.53691499</v>
+        <v>1.50052602</v>
       </c>
       <c r="O79">
-        <v>0.2920138481</v>
+        <v>0.2850999437999999</v>
       </c>
       <c r="P79">
-        <v>1.2449011419</v>
+        <v>1.2154260762</v>
       </c>
       <c r="Q79">
-        <v>1.9239011419</v>
+        <v>1.8944260762</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.211915575775992</v>
+        <v>0.2190797710105621</v>
       </c>
       <c r="T79">
-        <v>3.237901762632682</v>
+        <v>3.377545262464029</v>
       </c>
       <c r="U79">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V79">
         <v>0.19</v>
       </c>
       <c r="W79">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y79">
-        <v>3.502772360458693</v>
+        <v>3.306819436497674</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08869592962232366</v>
+        <v>0.08867210681616913</v>
       </c>
       <c r="C80">
-        <v>2.958266823444385</v>
+        <v>2.829741836202492</v>
       </c>
       <c r="D80">
-        <v>11.75606682344439</v>
+        <v>11.75764183620249</v>
       </c>
       <c r="E80">
-        <v>8.2378</v>
+        <v>8.367900000000001</v>
       </c>
       <c r="F80">
-        <v>10.1478</v>
+        <v>10.2779</v>
       </c>
       <c r="G80">
         <v>1.35</v>
@@ -7847,28 +7847,28 @@
         <v>2.151</v>
       </c>
       <c r="M80">
-        <v>0.65047398</v>
+        <v>0.6588133900000001</v>
       </c>
       <c r="N80">
-        <v>1.50052602</v>
+        <v>1.49218661</v>
       </c>
       <c r="O80">
-        <v>0.2850999437999999</v>
+        <v>0.2835154558999999</v>
       </c>
       <c r="P80">
-        <v>1.2154260762</v>
+        <v>1.2086711541</v>
       </c>
       <c r="Q80">
-        <v>1.8944260762</v>
+        <v>1.8876711541</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2190797710105621</v>
+        <v>0.2269262705531864</v>
       </c>
       <c r="T80">
-        <v>3.377545262464029</v>
+        <v>3.530488143231696</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.306819436497674</v>
+        <v>3.264960962617957</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08867210681616913</v>
+        <v>0.08864828401001464</v>
       </c>
       <c r="C81">
-        <v>2.829741836202492</v>
+        <v>2.701217271040131</v>
       </c>
       <c r="D81">
-        <v>11.75764183620249</v>
+        <v>11.75921727104013</v>
       </c>
       <c r="E81">
-        <v>8.367900000000001</v>
+        <v>8.498000000000001</v>
       </c>
       <c r="F81">
-        <v>10.2779</v>
+        <v>10.408</v>
       </c>
       <c r="G81">
         <v>1.35</v>
@@ -7929,28 +7929,28 @@
         <v>2.151</v>
       </c>
       <c r="M81">
-        <v>0.6588133900000001</v>
+        <v>0.6671528000000001</v>
       </c>
       <c r="N81">
-        <v>1.49218661</v>
+        <v>1.4838472</v>
       </c>
       <c r="O81">
-        <v>0.2835154558999999</v>
+        <v>0.2819309679999999</v>
       </c>
       <c r="P81">
-        <v>1.2086711541</v>
+        <v>1.201916232</v>
       </c>
       <c r="Q81">
-        <v>1.8876711541</v>
+        <v>1.880916232</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2269262705531864</v>
+        <v>0.2355574200500732</v>
       </c>
       <c r="T81">
-        <v>3.530488143231696</v>
+        <v>3.698725312076129</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.264960962617957</v>
+        <v>3.224148950585232</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08864828401001464</v>
+        <v>0.08862446120386011</v>
       </c>
       <c r="C82">
-        <v>2.701217271040131</v>
+        <v>2.572693128126987</v>
       </c>
       <c r="D82">
-        <v>11.75921727104013</v>
+        <v>11.76079312812699</v>
       </c>
       <c r="E82">
-        <v>8.498000000000001</v>
+        <v>8.6281</v>
       </c>
       <c r="F82">
-        <v>10.408</v>
+        <v>10.5381</v>
       </c>
       <c r="G82">
         <v>1.35</v>
@@ -8011,28 +8011,28 @@
         <v>2.151</v>
       </c>
       <c r="M82">
-        <v>0.6671528000000001</v>
+        <v>0.67549221</v>
       </c>
       <c r="N82">
-        <v>1.4838472</v>
+        <v>1.47550779</v>
       </c>
       <c r="O82">
-        <v>0.2819309679999999</v>
+        <v>0.2803464801</v>
       </c>
       <c r="P82">
-        <v>1.201916232</v>
+        <v>1.1951613099</v>
       </c>
       <c r="Q82">
-        <v>1.880916232</v>
+        <v>1.8741613099</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2355574200500732</v>
+        <v>0.2450971115992638</v>
       </c>
       <c r="T82">
-        <v>3.698725312076129</v>
+        <v>3.884671656588398</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.224148950585232</v>
+        <v>3.184344642553316</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08862446120386011</v>
+        <v>0.08860063839770559</v>
       </c>
       <c r="C83">
-        <v>2.572693128126987</v>
+        <v>2.444169407632842</v>
       </c>
       <c r="D83">
-        <v>11.76079312812699</v>
+        <v>11.76236940763284</v>
       </c>
       <c r="E83">
-        <v>8.6281</v>
+        <v>8.7582</v>
       </c>
       <c r="F83">
-        <v>10.5381</v>
+        <v>10.6682</v>
       </c>
       <c r="G83">
         <v>1.35</v>
@@ -8093,28 +8093,28 @@
         <v>2.151</v>
       </c>
       <c r="M83">
-        <v>0.67549221</v>
+        <v>0.6838316200000001</v>
       </c>
       <c r="N83">
-        <v>1.47550779</v>
+        <v>1.46716838</v>
       </c>
       <c r="O83">
-        <v>0.2803464801</v>
+        <v>0.2787619922</v>
       </c>
       <c r="P83">
-        <v>1.1951613099</v>
+        <v>1.1884063878</v>
       </c>
       <c r="Q83">
-        <v>1.8741613099</v>
+        <v>1.8674063878</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2450971115992638</v>
+        <v>0.2556967688761422</v>
       </c>
       <c r="T83">
-        <v>3.884671656588398</v>
+        <v>4.091278706046473</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.184344642553316</v>
+        <v>3.145511171302666</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08860063839770559</v>
+        <v>0.08857681559155108</v>
       </c>
       <c r="C84">
-        <v>2.444169407632842</v>
+        <v>2.315646109727567</v>
       </c>
       <c r="D84">
-        <v>11.76236940763284</v>
+        <v>11.76394610972757</v>
       </c>
       <c r="E84">
-        <v>8.7582</v>
+        <v>8.888300000000001</v>
       </c>
       <c r="F84">
-        <v>10.6682</v>
+        <v>10.7983</v>
       </c>
       <c r="G84">
         <v>1.35</v>
@@ -8175,28 +8175,28 @@
         <v>2.151</v>
       </c>
       <c r="M84">
-        <v>0.6838316200000001</v>
+        <v>0.6921710300000001</v>
       </c>
       <c r="N84">
-        <v>1.46716838</v>
+        <v>1.45882897</v>
       </c>
       <c r="O84">
-        <v>0.2787619922</v>
+        <v>0.2771775042999999</v>
       </c>
       <c r="P84">
-        <v>1.1884063878</v>
+        <v>1.1816514657</v>
       </c>
       <c r="Q84">
-        <v>1.8674063878</v>
+        <v>1.8606514657</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2556967688761422</v>
+        <v>0.2675434446561828</v>
       </c>
       <c r="T84">
-        <v>4.091278706046473</v>
+        <v>4.322192467205499</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.145511171302666</v>
+        <v>3.107613446347212</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08857681559155108</v>
+        <v>0.08855299278539658</v>
       </c>
       <c r="C85">
-        <v>2.315646109727567</v>
+        <v>2.187123234581122</v>
       </c>
       <c r="D85">
-        <v>11.76394610972757</v>
+        <v>11.76552323458112</v>
       </c>
       <c r="E85">
-        <v>8.888300000000001</v>
+        <v>9.018400000000002</v>
       </c>
       <c r="F85">
-        <v>10.7983</v>
+        <v>10.9284</v>
       </c>
       <c r="G85">
         <v>1.35</v>
@@ -8257,28 +8257,28 @@
         <v>2.151</v>
       </c>
       <c r="M85">
-        <v>0.6921710300000001</v>
+        <v>0.7005104400000002</v>
       </c>
       <c r="N85">
-        <v>1.45882897</v>
+        <v>1.45048956</v>
       </c>
       <c r="O85">
-        <v>0.2771775042999999</v>
+        <v>0.2755930163999999</v>
       </c>
       <c r="P85">
-        <v>1.1816514657</v>
+        <v>1.1748965436</v>
       </c>
       <c r="Q85">
-        <v>1.8606514657</v>
+        <v>1.8538965436</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2675434446561828</v>
+        <v>0.2808709549087287</v>
       </c>
       <c r="T85">
-        <v>4.322192467205499</v>
+        <v>4.581970448509405</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.107613446347212</v>
+        <v>3.070618048176411</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08855299278539658</v>
+        <v>0.08852916997924207</v>
       </c>
       <c r="C86">
-        <v>2.187123234581124</v>
+        <v>2.058600782363568</v>
       </c>
       <c r="D86">
-        <v>11.76552323458112</v>
+        <v>11.76710078236357</v>
       </c>
       <c r="E86">
-        <v>9.0184</v>
+        <v>9.148499999999999</v>
       </c>
       <c r="F86">
-        <v>10.9284</v>
+        <v>11.0585</v>
       </c>
       <c r="G86">
         <v>1.35</v>
@@ -8339,28 +8339,28 @@
         <v>2.151</v>
       </c>
       <c r="M86">
-        <v>0.7005104400000001</v>
+        <v>0.70884985</v>
       </c>
       <c r="N86">
-        <v>1.45048956</v>
+        <v>1.44215015</v>
       </c>
       <c r="O86">
-        <v>0.2755930163999999</v>
+        <v>0.2740085285</v>
       </c>
       <c r="P86">
-        <v>1.1748965436</v>
+        <v>1.1681416215</v>
       </c>
       <c r="Q86">
-        <v>1.8538965436</v>
+        <v>1.8471416215</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2808709549087285</v>
+        <v>0.2959754665282803</v>
       </c>
       <c r="T86">
-        <v>4.581970448509401</v>
+        <v>4.87638549398716</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.070618048176412</v>
+        <v>3.034493129962572</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08852916997924207</v>
+        <v>0.09393882717308755</v>
       </c>
       <c r="C87">
-        <v>2.058600782363568</v>
+        <v>1.580811092675159</v>
       </c>
       <c r="D87">
-        <v>11.76710078236357</v>
+        <v>11.41941109267516</v>
       </c>
       <c r="E87">
-        <v>9.148499999999999</v>
+        <v>9.278599999999999</v>
       </c>
       <c r="F87">
-        <v>11.0585</v>
+        <v>11.1886</v>
       </c>
       <c r="G87">
         <v>1.35</v>
@@ -8421,45 +8421,45 @@
         <v>2.151</v>
       </c>
       <c r="M87">
-        <v>0.70884985</v>
+        <v>0.80446034</v>
       </c>
       <c r="N87">
-        <v>1.44215015</v>
+        <v>1.34653966</v>
       </c>
       <c r="O87">
-        <v>0.2740085285</v>
+        <v>0.2558425354</v>
       </c>
       <c r="P87">
-        <v>1.1681416215</v>
+        <v>1.0906971246</v>
       </c>
       <c r="Q87">
-        <v>1.8471416215</v>
+        <v>1.7696971246</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2959754665282803</v>
+        <v>0.3132377655220538</v>
       </c>
       <c r="T87">
-        <v>4.87638549398716</v>
+        <v>5.212859831676026</v>
       </c>
       <c r="U87">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V87">
         <v>0.19</v>
       </c>
       <c r="W87">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y87">
-        <v>3.034493129962572</v>
+        <v>2.673842193388924</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09393882717308755</v>
+        <v>0.09397818436693303</v>
       </c>
       <c r="C88">
-        <v>1.580811092675159</v>
+        <v>1.448256795894693</v>
       </c>
       <c r="D88">
-        <v>11.41941109267516</v>
+        <v>11.41695679589469</v>
       </c>
       <c r="E88">
-        <v>9.278599999999999</v>
+        <v>9.4087</v>
       </c>
       <c r="F88">
-        <v>11.1886</v>
+        <v>11.3187</v>
       </c>
       <c r="G88">
         <v>1.35</v>
@@ -8503,28 +8503,28 @@
         <v>2.151</v>
       </c>
       <c r="M88">
-        <v>0.80446034</v>
+        <v>0.81381453</v>
       </c>
       <c r="N88">
-        <v>1.34653966</v>
+        <v>1.33718547</v>
       </c>
       <c r="O88">
-        <v>0.2558425354</v>
+        <v>0.2540652392999999</v>
       </c>
       <c r="P88">
-        <v>1.0906971246</v>
+        <v>1.0831202307</v>
       </c>
       <c r="Q88">
-        <v>1.7696971246</v>
+        <v>1.7621202307</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3132377655220538</v>
+        <v>0.3331558028225617</v>
       </c>
       <c r="T88">
-        <v>5.212859831676026</v>
+        <v>5.601099452086255</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.673842193388924</v>
+        <v>2.643108375074109</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09397818436693303</v>
+        <v>0.09401754156077852</v>
       </c>
       <c r="C89">
-        <v>1.448256795894693</v>
+        <v>1.315703553858349</v>
       </c>
       <c r="D89">
-        <v>11.41695679589469</v>
+        <v>11.41450355385835</v>
       </c>
       <c r="E89">
-        <v>9.4087</v>
+        <v>9.5388</v>
       </c>
       <c r="F89">
-        <v>11.3187</v>
+        <v>11.4488</v>
       </c>
       <c r="G89">
         <v>1.35</v>
@@ -8585,28 +8585,28 @@
         <v>2.151</v>
       </c>
       <c r="M89">
-        <v>0.81381453</v>
+        <v>0.8231687200000001</v>
       </c>
       <c r="N89">
-        <v>1.33718547</v>
+        <v>1.32783128</v>
       </c>
       <c r="O89">
-        <v>0.2540652392999999</v>
+        <v>0.2522879432</v>
       </c>
       <c r="P89">
-        <v>1.0831202307</v>
+        <v>1.0755433368</v>
       </c>
       <c r="Q89">
-        <v>1.7621202307</v>
+        <v>1.7545433368</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3331558028225617</v>
+        <v>0.3563935130064876</v>
       </c>
       <c r="T89">
-        <v>5.601099452086255</v>
+        <v>6.054045675898192</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.643108375074109</v>
+        <v>2.613073052630085</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09401754156077852</v>
+        <v>0.094056898754624</v>
       </c>
       <c r="C90">
-        <v>1.315703553858349</v>
+        <v>1.183151365886349</v>
       </c>
       <c r="D90">
-        <v>11.41450355385835</v>
+        <v>11.41205136588635</v>
       </c>
       <c r="E90">
-        <v>9.5388</v>
+        <v>9.668900000000001</v>
       </c>
       <c r="F90">
-        <v>11.4488</v>
+        <v>11.5789</v>
       </c>
       <c r="G90">
         <v>1.35</v>
@@ -8667,28 +8667,28 @@
         <v>2.151</v>
       </c>
       <c r="M90">
-        <v>0.8231687200000001</v>
+        <v>0.8325229100000001</v>
       </c>
       <c r="N90">
-        <v>1.32783128</v>
+        <v>1.31847709</v>
       </c>
       <c r="O90">
-        <v>0.2522879432</v>
+        <v>0.2505106470999999</v>
       </c>
       <c r="P90">
-        <v>1.0755433368</v>
+        <v>1.0679664429</v>
       </c>
       <c r="Q90">
-        <v>1.7545433368</v>
+        <v>1.7469664429</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3563935130064876</v>
+        <v>0.3838562614056727</v>
       </c>
       <c r="T90">
-        <v>6.054045675898192</v>
+        <v>6.589345758585024</v>
       </c>
       <c r="U90">
         <v>0.07190000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.613073052630085</v>
+        <v>2.583712681252218</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.094056898754624</v>
+        <v>0.09409625594846949</v>
       </c>
       <c r="C91">
-        <v>1.183151365886349</v>
+        <v>1.05060023129951</v>
       </c>
       <c r="D91">
-        <v>11.41205136588635</v>
+        <v>11.40960023129951</v>
       </c>
       <c r="E91">
-        <v>9.668900000000001</v>
+        <v>9.798999999999999</v>
       </c>
       <c r="F91">
-        <v>11.5789</v>
+        <v>11.709</v>
       </c>
       <c r="G91">
         <v>1.35</v>
@@ -8749,28 +8749,28 @@
         <v>2.151</v>
       </c>
       <c r="M91">
-        <v>0.8325229100000001</v>
+        <v>0.8418771</v>
       </c>
       <c r="N91">
-        <v>1.31847709</v>
+        <v>1.3091229</v>
       </c>
       <c r="O91">
-        <v>0.2505106470999999</v>
+        <v>0.248733351</v>
       </c>
       <c r="P91">
-        <v>1.0679664429</v>
+        <v>1.060389549</v>
       </c>
       <c r="Q91">
-        <v>1.7469664429</v>
+        <v>1.739389549</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3838562614056727</v>
+        <v>0.4168115594846949</v>
       </c>
       <c r="T91">
-        <v>6.589345758585024</v>
+        <v>7.231705857809224</v>
       </c>
       <c r="U91">
         <v>0.07190000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.583712681252218</v>
+        <v>2.555004762571639</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09409625594846949</v>
+        <v>0.09413561314231497</v>
       </c>
       <c r="C92">
-        <v>1.05060023129951</v>
+        <v>0.9180501494192157</v>
       </c>
       <c r="D92">
-        <v>11.40960023129951</v>
+        <v>11.40715014941922</v>
       </c>
       <c r="E92">
-        <v>9.798999999999999</v>
+        <v>9.9291</v>
       </c>
       <c r="F92">
-        <v>11.709</v>
+        <v>11.8391</v>
       </c>
       <c r="G92">
         <v>1.35</v>
@@ -8831,28 +8831,28 @@
         <v>2.151</v>
       </c>
       <c r="M92">
-        <v>0.8418771</v>
+        <v>0.8512312900000001</v>
       </c>
       <c r="N92">
-        <v>1.3091229</v>
+        <v>1.29976871</v>
       </c>
       <c r="O92">
-        <v>0.248733351</v>
+        <v>0.2469560548999999</v>
       </c>
       <c r="P92">
-        <v>1.060389549</v>
+        <v>1.0528126551</v>
       </c>
       <c r="Q92">
-        <v>1.739389549</v>
+        <v>1.7318126551</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4168115594846949</v>
+        <v>0.457090257136833</v>
       </c>
       <c r="T92">
-        <v>7.231705857809224</v>
+        <v>8.016812645749912</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.555004762571639</v>
+        <v>2.526927787158764</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09413561314231497</v>
+        <v>0.09708125033616047</v>
       </c>
       <c r="C93">
-        <v>0.9180501494192157</v>
+        <v>0.6075162864079999</v>
       </c>
       <c r="D93">
-        <v>11.40715014941922</v>
+        <v>11.226716286408</v>
       </c>
       <c r="E93">
-        <v>9.9291</v>
+        <v>10.0592</v>
       </c>
       <c r="F93">
-        <v>11.8391</v>
+        <v>11.9692</v>
       </c>
       <c r="G93">
         <v>1.35</v>
@@ -8913,45 +8913,45 @@
         <v>2.151</v>
       </c>
       <c r="M93">
-        <v>0.8512312900000001</v>
+        <v>0.9072653600000001</v>
       </c>
       <c r="N93">
-        <v>1.29976871</v>
+        <v>1.24373464</v>
       </c>
       <c r="O93">
-        <v>0.2469560548999999</v>
+        <v>0.2363095815999999</v>
       </c>
       <c r="P93">
-        <v>1.0528126551</v>
+        <v>1.0074250584</v>
       </c>
       <c r="Q93">
-        <v>1.7318126551</v>
+        <v>1.6864250584</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.457090257136833</v>
+        <v>0.507438629202006</v>
       </c>
       <c r="T93">
-        <v>8.016812645749912</v>
+        <v>8.998196130675776</v>
       </c>
       <c r="U93">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V93">
         <v>0.19</v>
       </c>
       <c r="W93">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y93">
-        <v>2.526927787158764</v>
+        <v>2.370860935327674</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09708125033616047</v>
+        <v>0.09715219753000595</v>
       </c>
       <c r="C94">
-        <v>0.6075162864079999</v>
+        <v>0.4731408132866797</v>
       </c>
       <c r="D94">
-        <v>11.226716286408</v>
+        <v>11.22244081328668</v>
       </c>
       <c r="E94">
-        <v>10.0592</v>
+        <v>10.1893</v>
       </c>
       <c r="F94">
-        <v>11.9692</v>
+        <v>12.0993</v>
       </c>
       <c r="G94">
         <v>1.35</v>
@@ -8995,28 +8995,28 @@
         <v>2.151</v>
       </c>
       <c r="M94">
-        <v>0.9072653600000001</v>
+        <v>0.9171269400000002</v>
       </c>
       <c r="N94">
-        <v>1.24373464</v>
+        <v>1.23387306</v>
       </c>
       <c r="O94">
-        <v>0.2363095815999999</v>
+        <v>0.2344358813999999</v>
       </c>
       <c r="P94">
-        <v>1.0074250584</v>
+        <v>0.9994371785999997</v>
       </c>
       <c r="Q94">
-        <v>1.6864250584</v>
+        <v>1.6784371786</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.507438629202006</v>
+        <v>0.5721722504286566</v>
       </c>
       <c r="T94">
-        <v>8.998196130675776</v>
+        <v>10.25997489700902</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.370860935327674</v>
+        <v>2.345367806990818</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09715219753000595</v>
+        <v>0.09722314472385143</v>
       </c>
       <c r="C95">
-        <v>0.4731408132866797</v>
+        <v>0.3387685953846304</v>
       </c>
       <c r="D95">
-        <v>11.22244081328668</v>
+        <v>11.21816859538463</v>
       </c>
       <c r="E95">
-        <v>10.1893</v>
+        <v>10.3194</v>
       </c>
       <c r="F95">
-        <v>12.0993</v>
+        <v>12.2294</v>
       </c>
       <c r="G95">
         <v>1.35</v>
@@ -9077,28 +9077,28 @@
         <v>2.151</v>
       </c>
       <c r="M95">
-        <v>0.9171269400000002</v>
+        <v>0.9269885200000001</v>
       </c>
       <c r="N95">
-        <v>1.23387306</v>
+        <v>1.22401148</v>
       </c>
       <c r="O95">
-        <v>0.2344358813999999</v>
+        <v>0.2325621811999999</v>
       </c>
       <c r="P95">
-        <v>0.9994371785999997</v>
+        <v>0.9914492987999998</v>
       </c>
       <c r="Q95">
-        <v>1.6784371786</v>
+        <v>1.6704492988</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5721722504286566</v>
+        <v>0.6584837453975242</v>
       </c>
       <c r="T95">
-        <v>10.25997489700902</v>
+        <v>11.94234658545336</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.345367806990818</v>
+        <v>2.320417085639852</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09722314472385143</v>
+        <v>0.09729409191769692</v>
       </c>
       <c r="C96">
-        <v>0.3387685953846304</v>
+        <v>0.2043996289856249</v>
       </c>
       <c r="D96">
-        <v>11.21816859538463</v>
+        <v>11.21389962898563</v>
       </c>
       <c r="E96">
-        <v>10.3194</v>
+        <v>10.4495</v>
       </c>
       <c r="F96">
-        <v>12.2294</v>
+        <v>12.3595</v>
       </c>
       <c r="G96">
         <v>1.35</v>
@@ -9159,28 +9159,28 @@
         <v>2.151</v>
       </c>
       <c r="M96">
-        <v>0.9269885200000001</v>
+        <v>0.9368501000000001</v>
       </c>
       <c r="N96">
-        <v>1.22401148</v>
+        <v>1.2141499</v>
       </c>
       <c r="O96">
-        <v>0.2325621811999999</v>
+        <v>0.230688481</v>
       </c>
       <c r="P96">
-        <v>0.9914492987999998</v>
+        <v>0.9834614189999998</v>
       </c>
       <c r="Q96">
-        <v>1.6704492988</v>
+        <v>1.662461419</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6584837453975242</v>
+        <v>0.779319838353939</v>
       </c>
       <c r="T96">
-        <v>11.94234658545336</v>
+        <v>14.29766694927543</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.320417085639852</v>
+        <v>2.295991642633116</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09729409191769692</v>
+        <v>0.0973650391115424</v>
       </c>
       <c r="C97">
-        <v>0.2043996289856249</v>
+        <v>0.07003391037909346</v>
       </c>
       <c r="D97">
-        <v>11.21389962898563</v>
+        <v>11.20963391037909</v>
       </c>
       <c r="E97">
-        <v>10.4495</v>
+        <v>10.5796</v>
       </c>
       <c r="F97">
-        <v>12.3595</v>
+        <v>12.4896</v>
       </c>
       <c r="G97">
         <v>1.35</v>
@@ -9241,28 +9241,28 @@
         <v>2.151</v>
       </c>
       <c r="M97">
-        <v>0.9368501000000001</v>
+        <v>0.9467116800000002</v>
       </c>
       <c r="N97">
-        <v>1.2141499</v>
+        <v>1.20428832</v>
       </c>
       <c r="O97">
-        <v>0.230688481</v>
+        <v>0.2288147807999999</v>
       </c>
       <c r="P97">
-        <v>0.9834614189999998</v>
+        <v>0.9754735391999997</v>
       </c>
       <c r="Q97">
-        <v>1.662461419</v>
+        <v>1.6544735392</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.779319838353939</v>
+        <v>0.9605739777885617</v>
       </c>
       <c r="T97">
-        <v>14.29766694927543</v>
+        <v>17.83064749500854</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.295991642633116</v>
+        <v>2.272075063022355</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.0973650391115424</v>
+        <v>0.0974359863053879</v>
       </c>
       <c r="C98">
-        <v>0.07003391037909523</v>
+        <v>-0.06432856413989541</v>
       </c>
       <c r="D98">
-        <v>11.20963391037909</v>
+        <v>11.2053714358601</v>
       </c>
       <c r="E98">
-        <v>10.5796</v>
+        <v>10.7097</v>
       </c>
       <c r="F98">
-        <v>12.4896</v>
+        <v>12.6197</v>
       </c>
       <c r="G98">
         <v>1.35</v>
@@ -9323,28 +9323,28 @@
         <v>2.151</v>
       </c>
       <c r="M98">
-        <v>0.9467116800000001</v>
+        <v>0.9565732600000001</v>
       </c>
       <c r="N98">
-        <v>1.20428832</v>
+        <v>1.19442674</v>
       </c>
       <c r="O98">
-        <v>0.2288147808</v>
+        <v>0.2269410806</v>
       </c>
       <c r="P98">
-        <v>0.9754735391999999</v>
+        <v>0.9674856593999998</v>
       </c>
       <c r="Q98">
-        <v>1.6544735392</v>
+        <v>1.6464856594</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9605739777885591</v>
+        <v>1.262664210179595</v>
       </c>
       <c r="T98">
-        <v>17.83064749500849</v>
+        <v>23.71894840456364</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.272075063022355</v>
+        <v>2.248651608764392</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.0974359863053879</v>
+        <v>0.09750693349923339</v>
       </c>
       <c r="C99">
-        <v>-0.06432856413989541</v>
+        <v>-0.1986877982706368</v>
       </c>
       <c r="D99">
-        <v>11.2053714358601</v>
+        <v>11.20111220172936</v>
       </c>
       <c r="E99">
-        <v>10.7097</v>
+        <v>10.8398</v>
       </c>
       <c r="F99">
-        <v>12.6197</v>
+        <v>12.7498</v>
       </c>
       <c r="G99">
         <v>1.35</v>
@@ -9405,28 +9405,28 @@
         <v>2.151</v>
       </c>
       <c r="M99">
-        <v>0.9565732600000001</v>
+        <v>0.96643484</v>
       </c>
       <c r="N99">
-        <v>1.19442674</v>
+        <v>1.18456516</v>
       </c>
       <c r="O99">
-        <v>0.2269410806</v>
+        <v>0.2250673804</v>
       </c>
       <c r="P99">
-        <v>0.9674856593999998</v>
+        <v>0.9594977795999998</v>
       </c>
       <c r="Q99">
-        <v>1.6464856594</v>
+        <v>1.6384977796</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.262664210179595</v>
+        <v>1.866844674961667</v>
       </c>
       <c r="T99">
-        <v>23.71894840456364</v>
+        <v>35.49555022367395</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.248651608764392</v>
+        <v>2.225706184185164</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09750693349923339</v>
+        <v>0.09757788069307886</v>
       </c>
       <c r="C100">
-        <v>-0.1986877982706368</v>
+        <v>-0.3330437957068053</v>
       </c>
       <c r="D100">
-        <v>11.20111220172936</v>
+        <v>11.19685620429319</v>
       </c>
       <c r="E100">
-        <v>10.8398</v>
+        <v>10.9699</v>
       </c>
       <c r="F100">
-        <v>12.7498</v>
+        <v>12.8799</v>
       </c>
       <c r="G100">
         <v>1.35</v>
@@ -9487,28 +9487,28 @@
         <v>2.151</v>
       </c>
       <c r="M100">
-        <v>0.96643484</v>
+        <v>0.9762964200000001</v>
       </c>
       <c r="N100">
-        <v>1.18456516</v>
+        <v>1.17470358</v>
       </c>
       <c r="O100">
-        <v>0.2250673804</v>
+        <v>0.2231936801999999</v>
       </c>
       <c r="P100">
-        <v>0.9594977795999998</v>
+        <v>0.9515098997999997</v>
       </c>
       <c r="Q100">
-        <v>1.6384977796</v>
+        <v>1.6305098998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.866844674961667</v>
+        <v>3.679386069307883</v>
       </c>
       <c r="T100">
-        <v>35.49555022367395</v>
+        <v>70.82535568100487</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.225706184185164</v>
+        <v>2.203224303536829</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09757788069307886</v>
-      </c>
-      <c r="C101">
-        <v>-0.3330437957068053</v>
-      </c>
-      <c r="D101">
-        <v>11.19685620429319</v>
-      </c>
-      <c r="E101">
-        <v>10.9699</v>
-      </c>
-      <c r="F101">
-        <v>12.8799</v>
-      </c>
-      <c r="G101">
-        <v>1.35</v>
-      </c>
-      <c r="H101">
-        <v>11.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.83</v>
-      </c>
-      <c r="K101">
-        <v>0.679</v>
-      </c>
-      <c r="L101">
-        <v>2.151</v>
-      </c>
-      <c r="M101">
-        <v>0.9762964200000001</v>
-      </c>
-      <c r="N101">
-        <v>1.17470358</v>
-      </c>
-      <c r="O101">
-        <v>0.2231936801999999</v>
-      </c>
-      <c r="P101">
-        <v>0.9515098997999997</v>
-      </c>
-      <c r="Q101">
-        <v>1.6305098998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.679386069307883</v>
-      </c>
-      <c r="T101">
-        <v>70.82535568100487</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.19</v>
-      </c>
-      <c r="W101">
-        <v>0.06139800000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.203224303536829</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
